--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -1047,7 +1047,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-22</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-22</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-22</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-22</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>12 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>5 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-22</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>5 days ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>RUEL</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B7" t="str">
-        <v>5 days ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-22</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>5 days ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>TINI</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-22</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Evanescence</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-22</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-22</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Armin van Buuren</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-22</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Madison Cunningham</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-22</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Johnny Orlando</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B13" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-22</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Carver Jones</v>
+        <v>kesha</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B14" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-22</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Jazmin bean</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-22</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Baby Queen</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B16" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-22</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Switchfoot</v>
+        <v>The Analogues</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-22</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Grace Potter</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-22</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Blue October</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-22</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>The All-American Rejects</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-22</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Henry Moodie</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-22</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Spacey Jane</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-22</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Megan Moroney</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-22</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Matt Hansen</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-22</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Matt Hansen</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-22</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Keith Urban</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-22</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>VALÉ</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-22</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-22</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Towa Bird</v>
+        <v>Evanescence</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-22</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Sabrina Sterling</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-22</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Little Big Town</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-22</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Becky G</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-22</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Daisy the Great</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-22</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Towa Bird</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-22</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Madonna</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B35" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-22</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Ally Salort</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B36" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-22</v>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Bella White</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B37" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-22</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B38" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-22</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Towa Bird</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-22</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Miranda Lambert</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B40" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-22</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Lady Gaga</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-22</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Gracie Abrams</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-22</v>
@@ -1977,7 +1977,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-22</v>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Martin Garrix</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-22</v>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Jorja Smith</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-22</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>LP</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-22</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>The Rolling Stones</v>
+        <v>VALÉ</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-22</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Oasis</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-22</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-22</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>VictorBiliac</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-22</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Linkin Park</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-22</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Harry Styles</v>
+        <v>Becky G</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-22</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Eagles</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-22</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Nora Fatehi</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B54" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-22</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Madonna</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-22</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B56" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-22</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 months ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Bella White</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-22</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>The Head And The Heart</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-22</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Simply Red</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-22</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Talking Heads</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B60" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-22</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Ellise</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-22</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Tori Kelly</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-22</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>David Gilmour</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-22</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Scorpions</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B64" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-22</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>13 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Claire Leslie</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-22</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Michael Schulte</v>
+        <v>LP</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-22</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Caity Baser</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-22</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Sam Fischer</v>
+        <v>Oasis</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-22</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Porches</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-22</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Charli xcx</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-22</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Jon Batiste</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B71" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-22</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B72" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-22</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Eagles</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-22</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Bruno Mars</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-22</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Tori Kelly</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-22</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>bea miller</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-22</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>The Chainsmokers</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-22</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Madison Beer</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B78" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-22</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Tori Kelly</v>
+        <v>Simply Red</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-22</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-22</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>The Chainsmokers</v>
+        <v>Ellise</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-22</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ashley Cooke</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ari Abdul - Ego (Visualizer)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B82" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-22</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Ari Abdul</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B83" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-22</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Quinn XCII</v>
+        <v>Scorpions</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B84" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-22</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Madison Beer</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-22</v>
@@ -3611,7 +3611,7 @@
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>David J</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-22</v>
@@ -3649,7 +3649,7 @@
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B87" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-22</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Ocean Alley</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-22</v>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Dagny</v>
+        <v>Porches</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-22</v>
@@ -3763,7 +3763,7 @@
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B90" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-22</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Paris Paloma</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lucy Blue - Who you love (Visualiser)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-22</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Lucy Blue</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-22</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Olivia Dean</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-22</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Aaron Frazer</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B94" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-22</v>
@@ -3953,7 +3953,7 @@
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Holly Humberstone</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>DANNA - OUT OF MY BODY</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-22</v>
@@ -3991,7 +3991,7 @@
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Danna</v>
+        <v>bea miller</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>DANNA - OUT OF MY BODY - Danna</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B96" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-22</v>
@@ -4029,7 +4029,7 @@
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Rolling Stones</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-22</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-22</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-22</v>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Rick Astley</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-22</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Jessie J</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-22</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>The Takes</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B3" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>12 hours ago</v>
+        <v>14 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B7" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>17 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B3" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>14 hours ago</v>
+        <v>16 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B7" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>16 hours ago</v>
+        <v>18 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>18 hours ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B7" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>18 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>19 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-23</v>
       </c>
       <c r="E199" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>20 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -971,7 +971,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -743,7 +743,7 @@
         <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Dean Lewis</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-23</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Niall Horan</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Will Linley</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-23</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>RUEL</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>TINI</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Charli xcx</v>
+        <v>The Offspring</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-23</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Dua Lipa</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-23</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Matilda Mann</v>
+        <v>Scorpions</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-23</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Ella Langley</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>kesha</v>
+        <v>The Warning</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Holly Humberstone</v>
+        <v>paris jackson</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Foo Fighters</v>
+        <v>Minelli</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>The Analogues</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Rod Stewart</v>
+        <v>David Guetta</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Blue October</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Far Caspian</v>
+        <v>Lauv</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Kenia Os</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B23" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>RUEL</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B27" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>6 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>TINI</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Evanescence</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B29" t="str">
-        <v>10 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-23</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>10 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-23</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Armin van Buuren</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B31" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-23</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>6 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Madison Cunningham</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-23</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Johnny Orlando</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B33" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-23</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Carver Jones</v>
+        <v>kesha</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B34" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-23</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Jazmin bean</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-23</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Baby Queen</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B36" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-23</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>7 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Switchfoot</v>
+        <v>The Analogues</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Grace Potter</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Blue October</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>The All-American Rejects</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B40" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Henry Moodie</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B41" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>8 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Spacey Jane</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Megan Moroney</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B43" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Matt Hansen</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Matt Hansen</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Keith Urban</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>VALÉ</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B48" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-23</v>
@@ -2205,7 +2205,7 @@
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Towa Bird</v>
+        <v>Evanescence</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Sabrina Sterling</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Little Big Town</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Becky G</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Daisy the Great</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Towa Bird</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Madonna</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Ally Salort</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-23</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Bella White</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-23</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-23</v>
@@ -2585,7 +2585,7 @@
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Towa Bird</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-23</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Miranda Lambert</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-23</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Lady Gaga</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-23</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Gracie Abrams</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-23</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-23</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Martin Garrix</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-23</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Jorja Smith</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-23</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>LP</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-23</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>The Rolling Stones</v>
+        <v>VALÉ</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-23</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Oasis</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-23</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-23</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>VictorBiliac</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-23</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Linkin Park</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-23</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Harry Styles</v>
+        <v>Becky G</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-23</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Eagles</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-23</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Nora Fatehi</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B74" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Madonna</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-23</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B76" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-23</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 months ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Bella White</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>The Head And The Heart</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-23</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Simply Red</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Talking Heads</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-23</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Ellise</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-23</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Tori Kelly</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-23</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>David Gilmour</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-23</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Scorpions</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Claire Leslie</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Michael Schulte - Lovesick (Official Video)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Michael Schulte</v>
+        <v>LP</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Caity Baser - Holiday Song (Official Video)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Caity Baser</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Sam Fischer</v>
+        <v>Oasis</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Porches- HABIT (Official Video)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Porches</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Porches- HABIT (Official Video) - Porches</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Charli xcx - Rock Music (Official Video)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Charli xcx</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Jon Batiste - Alla Blues (Audio)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-23</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Jon Batiste</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-23</v>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Tigirlily Gold</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B92" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-23</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Eagles</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-23</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Bruno Mars</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tori Kelly - Control (Official Visualizer)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-23</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Tori Kelly</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-23</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>bea miller</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-23</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>The Chainsmokers</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Madison Beer - free (Official Audio)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-23</v>
@@ -4067,7 +4067,7 @@
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Madison Beer</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Tori Kelly - Dive (Official Audio)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-23</v>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Tori Kelly</v>
+        <v>Simply Red</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-23</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>JeremyCampMusic</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-23</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>The Chainsmokers</v>
+        <v>Ellise</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ashley Cooke - high school sweetheart</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-23</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Ashley Cooke</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19 hours ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 hours ago</v>
+        <v>3 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B10" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 hours ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B29" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B84" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B2" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v>9 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B83" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 hours ago</v>
+        <v>10 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>10 hours ago</v>
+        <v>13 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-24</v>
       </c>
       <c r="E199" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>13 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>13 hours ago</v>
+        <v>17 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B74" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B76" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B78" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B80" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B4" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>17 hours ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-24</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Duran Duran</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-24</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>20 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Nico Santos</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B4" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-24</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-24</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Will Linley</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-24</v>
@@ -609,7 +609,7 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Kylie Minogue</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B7" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-24</v>
@@ -647,7 +647,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Billy Raffoul</v>
+        <v>Will Linley</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-24</v>
@@ -685,7 +685,7 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Offspring</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-24</v>
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>David Gilmour</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B10" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-24</v>
@@ -761,7 +761,7 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Scorpions</v>
+        <v>The Offspring</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B11" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-24</v>
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Brandon Lake</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B12" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-24</v>
@@ -837,7 +837,7 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Scorpions</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B13" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-24</v>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>The Warning</v>
+        <v>Brandon Lake</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-24</v>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>paris jackson</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B15" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-24</v>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Minelli</v>
+        <v>The Warning</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-24</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Maggie Rose</v>
+        <v>paris jackson</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-24</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>David Guetta</v>
+        <v>Minelli</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-24</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-24</v>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Lauv</v>
+        <v>David Guetta</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-24</v>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Icona Pop</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-24</v>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Will Swinton</v>
+        <v>Lauv</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-24</v>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Dean Lewis</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-24</v>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-24</v>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Niall Horan</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-24</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-24</v>
@@ -1369,7 +1369,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>RUEL</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-24</v>
@@ -1407,7 +1407,7 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>TINI</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-24</v>
@@ -1445,7 +1445,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Charli xcx</v>
+        <v>RUEL</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B29" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-24</v>
@@ -1483,7 +1483,7 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Dua Lipa</v>
+        <v>TINI</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B30" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-24</v>
@@ -1521,7 +1521,7 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Matilda Mann</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-24</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Ella Langley</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-24</v>
@@ -1597,7 +1597,7 @@
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-24</v>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>kesha</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-24</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Holly Humberstone</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-24</v>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Foo Fighters</v>
+        <v>kesha</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-24</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>The Analogues</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-24</v>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Rod Stewart</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-24</v>
@@ -1825,7 +1825,7 @@
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Blue October</v>
+        <v>The Analogues</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-24</v>
@@ -1863,7 +1863,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Far Caspian</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-24</v>
@@ -1901,7 +1901,7 @@
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Kenia Os</v>
+        <v>Blue October</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-24</v>
@@ -1939,7 +1939,7 @@
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-24</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-24</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-24</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-24</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B46" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-24</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B47" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-24</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-24</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Evanescence</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-24</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-24</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Armin van Buuren</v>
+        <v>Evanescence</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-24</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Madison Cunningham</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-24</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Johnny Orlando</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-24</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Carver Jones</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-24</v>
@@ -2433,7 +2433,7 @@
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Jazmin bean</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-24</v>
@@ -2471,7 +2471,7 @@
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Baby Queen</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-24</v>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Switchfoot</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-24</v>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Grace Potter</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-24</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B59" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-24</v>
@@ -2623,7 +2623,7 @@
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>The All-American Rejects</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-24</v>
@@ -2661,7 +2661,7 @@
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Henry Moodie</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-24</v>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Spacey Jane</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-24</v>
@@ -2737,7 +2737,7 @@
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Megan Moroney</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-24</v>
@@ -2775,7 +2775,7 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Matt Hansen</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-24</v>
@@ -2813,7 +2813,7 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Matt Hansen</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-24</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Keith Urban</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-24</v>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>VALÉ</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-24</v>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-24</v>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Towa Bird</v>
+        <v>VALÉ</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-24</v>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-24</v>
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Little Big Town</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-24</v>
@@ -3079,7 +3079,7 @@
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Becky G</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-24</v>
@@ -3117,7 +3117,7 @@
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Daisy the Great</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-24</v>
@@ -3155,7 +3155,7 @@
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Towa Bird</v>
+        <v>Becky G</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-24</v>
@@ -3193,7 +3193,7 @@
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Madonna</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-24</v>
@@ -3231,7 +3231,7 @@
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Ally Salort</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-24</v>
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Bella White</v>
+        <v>Madonna</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-24</v>
@@ -3307,7 +3307,7 @@
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-24</v>
@@ -3345,7 +3345,7 @@
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Towa Bird</v>
+        <v>Bella White</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-24</v>
@@ -3383,7 +3383,7 @@
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Miranda Lambert</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B80" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-24</v>
@@ -3421,7 +3421,7 @@
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Lady Gaga</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B81" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-24</v>
@@ -3459,7 +3459,7 @@
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Gracie Abrams</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B82" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-24</v>
@@ -3497,7 +3497,7 @@
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-24</v>
@@ -3535,7 +3535,7 @@
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Martin Garrix</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-24</v>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Jorja Smith</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B85" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-24</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>LP</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-24</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>The Rolling Stones</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-24</v>
@@ -3687,7 +3687,7 @@
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Oasis</v>
+        <v>LP</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-24</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Breaking Benjamin</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-24</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>VictorBiliac</v>
+        <v>Oasis</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B90" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-24</v>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Linkin Park</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-24</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Harry Styles</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-24</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Eagles</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-24</v>
@@ -3915,7 +3915,7 @@
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Nora Fatehi</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-24</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Eagles</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B95" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-24</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B96" t="str">
         <v>2 months ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-24</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-24</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>The Head And The Heart</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-24</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Simply Red</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-24</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Talking Heads</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ellise - Liplock (Official Music Video)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B100" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-24</v>
@@ -4181,7 +4181,7 @@
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Ellise</v>
+        <v>Simply Red</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Tori Kelly - Dive (Official Music Video)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-24</v>
@@ -4219,7 +4219,7 @@
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Tori Kelly</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-24</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Lainey Wilson</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B3" t="str">
-        <v>20 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-24</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>20 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,7 +507,7 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B5" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B89" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>23 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B49" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B88" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B92" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B96" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B97" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B98" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B4" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B5" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B10" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B11" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B12" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B13" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B17" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B19" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B31" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B33" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B35" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B36" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B38" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B42" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B43" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B45" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B46" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B47" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B48" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B49" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B57" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B60" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B76" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B78" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B80" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B85" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B86" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B88" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B89" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B91" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B92" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B96" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B97" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B98" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -1313,7 +1313,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-24</v>
+        <v>2026-05-25</v>
       </c>
       <c r="E199" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -1085,7 +1085,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -1047,7 +1047,7 @@
         <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -591,7 +591,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B91" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B92" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>From Down Here</v>
+        <v>STOP</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-25</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>From Down Here - Single</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>4:01</v>
+        <v>2:56</v>
       </c>
       <c r="H102" t="str">
-        <v>Lola Young</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L102" t="str">
-        <v>From Down Here - Lola Young</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>the cure</v>
+        <v>From Down Here</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
+        <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-25</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>From Down Here - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>4:57</v>
+        <v>4:01</v>
       </c>
       <c r="H103" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Lola Young</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/lola-young/452271760</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
+        <v>https://music.apple.com/us/album/from-down-here/6768357139</v>
       </c>
       <c r="L103" t="str">
-        <v>the cure - Olivia Rodrigo</v>
+        <v>From Down Here - Lola Young</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SS26</v>
+        <v>the cure</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/ss26/6771061782</v>
+        <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-25</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>SS26 - Single</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G104" t="str">
-        <v>2:47</v>
+        <v>4:57</v>
       </c>
       <c r="H104" t="str">
-        <v>Charli xcx</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/ss26/6771061771</v>
+        <v>https://music.apple.com/us/album/the-cure/1889992111</v>
       </c>
       <c r="L104" t="str">
-        <v>SS26 - Charli xcx</v>
+        <v>the cure - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>White Flag</v>
+        <v>SS26</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
+        <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-25</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Cry Baby</v>
+        <v>SS26 - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:34</v>
+        <v>2:47</v>
       </c>
       <c r="H105" t="str">
-        <v>Vince Staples</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
+        <v>https://music.apple.com/us/album/ss26/6771061771</v>
       </c>
       <c r="L105" t="str">
-        <v>White Flag - Vince Staples</v>
+        <v>SS26 - Charli xcx</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Knew Better Part Two</v>
+        <v>White Flag</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
+        <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-25</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
+        <v>Cry Baby</v>
       </c>
       <c r="G106" t="str">
-        <v>2:44</v>
+        <v>2:34</v>
       </c>
       <c r="H106" t="str">
-        <v>Ariana Grande</v>
+        <v>Vince Staples</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
+        <v>https://music.apple.com/us/artist/vince-staples/566639154</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
+        <v>https://music.apple.com/us/album/white-flag/1887627836</v>
       </c>
       <c r="L106" t="str">
-        <v>Knew Better Part Two - Ariana Grande</v>
+        <v>White Flag - Vince Staples</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Goals</v>
+        <v>Knew Better Part Two</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/goals/6769251838</v>
+        <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-25</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Goals (FIFA World Cup 2026™) - Single</v>
+        <v>Dangerous Woman (Tenth Anniversary Edition)</v>
       </c>
       <c r="G107" t="str">
-        <v>3:00</v>
+        <v>2:44</v>
       </c>
       <c r="H107" t="str">
-        <v>LISA</v>
+        <v>Ariana Grande</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
+        <v>https://music.apple.com/us/artist/ariana-grande/412778295</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/goals/6769251829</v>
+        <v>https://music.apple.com/us/album/knew-better-part-two/6770600996</v>
       </c>
       <c r="L107" t="str">
-        <v>Goals - LISA</v>
+        <v>Knew Better Part Two - Ariana Grande</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>we should talk</v>
+        <v>Goals</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-25</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>everyone for ten minutes</v>
+        <v>Goals (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:04</v>
+        <v>3:00</v>
       </c>
       <c r="H108" t="str">
-        <v>Bleachers</v>
+        <v>LISA</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/lisa/1583908668</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v>https://music.apple.com/us/album/goals/6769251829</v>
       </c>
       <c r="L108" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>Goals - LISA</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>we should talk</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-25</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G109" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H109" t="str">
-        <v>The Band CAMINO</v>
+        <v>Bleachers</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
       </c>
       <c r="L109" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>we should talk - Bleachers</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Ego</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-25</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Ego - Single</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G110" t="str">
-        <v>2:53</v>
+        <v>3:26</v>
       </c>
       <c r="H110" t="str">
-        <v>The Warning</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L110" t="str">
-        <v>Ego - The Warning</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>Ego</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-25</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H111" t="str">
-        <v>Kylie Minogue</v>
+        <v>The Warning</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L111" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>All That Matters</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-25</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:43</v>
+        <v>3:17</v>
       </c>
       <c r="H112" t="str">
-        <v>6LACK</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L112" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Like A Virgin</v>
+        <v>All That Matters</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-25</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Terrified .</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G113" t="str">
-        <v>2:34</v>
+        <v>3:43</v>
       </c>
       <c r="H113" t="str">
-        <v>fakemink</v>
+        <v>6LACK</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L113" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>24 Hours</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-25</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>24 Hours - Single</v>
+        <v>Terrified .</v>
       </c>
       <c r="G114" t="str">
-        <v>3:17</v>
+        <v>2:34</v>
       </c>
       <c r="H114" t="str">
-        <v>Stormzy</v>
+        <v>fakemink</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L114" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>24 Hours</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-25</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:09</v>
+        <v>3:17</v>
       </c>
       <c r="H115" t="str">
-        <v>Lizzo</v>
+        <v>Stormzy</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L115" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Ms. Tundra</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-25</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Highway 79</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:12</v>
+        <v>2:09</v>
       </c>
       <c r="H116" t="str">
-        <v>Ne-Yo</v>
+        <v>Lizzo</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L116" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>TARENTINO</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-25</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>TARENTINO - Single</v>
+        <v>Highway 79</v>
       </c>
       <c r="G117" t="str">
-        <v>2:23</v>
+        <v>3:12</v>
       </c>
       <c r="H117" t="str">
-        <v>Labrinth</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L117" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Daydreamin’</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-25</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:58</v>
+        <v>2:23</v>
       </c>
       <c r="H118" t="str">
-        <v>ZAYN</v>
+        <v>Labrinth</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L118" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>End of an Era</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-25</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Dinner Party</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G119" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H119" t="str">
-        <v>Niall Horan</v>
+        <v>ZAYN</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L119" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Questions</v>
+        <v>End of an Era</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-25</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Florescence</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G120" t="str">
-        <v>3:07</v>
+        <v>3:38</v>
       </c>
       <c r="H120" t="str">
-        <v>Maisie Peters</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L120" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Questions</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-25</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G121" t="str">
-        <v>3:12</v>
+        <v>3:07</v>
       </c>
       <c r="H121" t="str">
-        <v>Blondshell</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L121" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-25</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:44</v>
+        <v>3:12</v>
       </c>
       <c r="H122" t="str">
-        <v>Kygo</v>
+        <v>Blondshell</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
       </c>
       <c r="L122" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>Heart Has To Work So Hard - Blondshell</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-25</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>OMAKASE</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:03</v>
+        <v>3:44</v>
       </c>
       <c r="H123" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Kygo</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
       </c>
       <c r="L123" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Dosis</v>
+        <v>PERDISTE EL EMMY.</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-25</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>DOSIS</v>
+        <v>OMAKASE</v>
       </c>
       <c r="G124" t="str">
-        <v>3:00</v>
+        <v>4:03</v>
       </c>
       <c r="H124" t="str">
-        <v>Xavi</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
       </c>
       <c r="L124" t="str">
-        <v>Dosis - Xavi</v>
+        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Would U Still Love Me</v>
+        <v>Dosis</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-25</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>DOSIS</v>
       </c>
       <c r="G125" t="str">
-        <v>2:36</v>
+        <v>3:00</v>
       </c>
       <c r="H125" t="str">
-        <v>Diplo</v>
+        <v>Xavi</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/dosis/1895081885</v>
       </c>
       <c r="L125" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>Dosis - Xavi</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Saving This Bottle</v>
+        <v>Would U Still Love Me</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-25</v>
@@ -5166,7 +5166,7 @@
         <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:05</v>
+        <v>2:36</v>
       </c>
       <c r="H126" t="str">
         <v>Diplo</v>
@@ -5178,21 +5178,21 @@
         <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
       </c>
       <c r="L126" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>Would U Still Love Me - Diplo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>The Climb</v>
+        <v>Saving This Bottle</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-25</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>The Climb - Single</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:50</v>
+        <v>3:05</v>
       </c>
       <c r="H127" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Diplo</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
       </c>
       <c r="L127" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>Saving This Bottle - Diplo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>everything tatted</v>
+        <v>The Climb</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-25</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>everything tatted - Single</v>
+        <v>The Climb - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:25</v>
+        <v>3:50</v>
       </c>
       <c r="H128" t="str">
-        <v>mgk</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
       </c>
       <c r="L128" t="str">
-        <v>everything tatted - mgk</v>
+        <v>The Climb - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>BOOMPALA</v>
+        <v>everything tatted</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-25</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>everything tatted - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:56</v>
+        <v>3:25</v>
       </c>
       <c r="H129" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
       </c>
       <c r="L129" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>everything tatted - mgk</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>BOOMPALA</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-25</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>can we do it all again?</v>
+        <v>'PUREFLOW', Pt. 1</v>
       </c>
       <c r="G130" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H130" t="str">
-        <v>Sonny Fodera</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/boompala/1894802719</v>
       </c>
       <c r="L130" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>BOOMPALA - LE SSERAFIM</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>Let Me Be In Your Arms</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-25</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>can we do it all again?</v>
       </c>
       <c r="G131" t="str">
-        <v>2:28</v>
+        <v>3:13</v>
       </c>
       <c r="H131" t="str">
-        <v>Sheff G</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
       </c>
       <c r="L131" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>Let Me Be In Your Arms - Sonny Fodera</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>touch myself</v>
+        <v>Eat, Work, Pray</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-25</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>and all pride aside</v>
+        <v>Eat, Work, Pray - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>4:09</v>
+        <v>2:28</v>
       </c>
       <c r="H132" t="str">
-        <v>kwn</v>
+        <v>Sheff G</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
       </c>
       <c r="L132" t="str">
-        <v>touch myself - kwn</v>
+        <v>Eat, Work, Pray - Sheff G</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Comes and Goes</v>
+        <v>touch myself</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-25</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>and all pride aside</v>
       </c>
       <c r="G133" t="str">
-        <v>4:22</v>
+        <v>4:09</v>
       </c>
       <c r="H133" t="str">
-        <v>KETTAMA</v>
+        <v>kwn</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
       </c>
       <c r="L133" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>touch myself - kwn</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Dear God</v>
+        <v>Comes and Goes</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-25</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Dear God</v>
+        <v>Comes and Goes - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>6:08</v>
+        <v>4:22</v>
       </c>
       <c r="H134" t="str">
-        <v>The Pretty Reckless</v>
+        <v>KETTAMA</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
       </c>
       <c r="L134" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>Comes and Goes - KETTAMA</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Hexagons</v>
+        <v>Dear God</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-25</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>The Wow! Signal</v>
+        <v>Dear God</v>
       </c>
       <c r="G135" t="str">
-        <v>5:26</v>
+        <v>6:08</v>
       </c>
       <c r="H135" t="str">
-        <v>Muse</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
       </c>
       <c r="L135" t="str">
-        <v>Hexagons - Muse</v>
+        <v>Dear God - The Pretty Reckless</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Facile-Batiste</v>
+        <v>Hexagons</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-25</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Black Mozart</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G136" t="str">
-        <v>4:55</v>
+        <v>5:26</v>
       </c>
       <c r="H136" t="str">
-        <v>Jon Batiste</v>
+        <v>Muse</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
       </c>
       <c r="L136" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Hexagons - Muse</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pop Pop</v>
+        <v>Facile-Batiste</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-25</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Pop Pop - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G137" t="str">
-        <v>2:57</v>
+        <v>4:55</v>
       </c>
       <c r="H137" t="str">
-        <v>Channel Tres</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
       </c>
       <c r="L137" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>Facile-Batiste - Jon Batiste</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>One Of Us</v>
+        <v>Pop Pop</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-25</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>One Of Us - Single</v>
+        <v>Pop Pop - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:35</v>
+        <v>2:57</v>
       </c>
       <c r="H138" t="str">
-        <v>Chris Young</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
       </c>
       <c r="L138" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>Pop Pop - Channel Tres</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Sins of the Father</v>
+        <v>One Of Us</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-25</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>One Of Us - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:20</v>
+        <v>3:35</v>
       </c>
       <c r="H139" t="str">
-        <v>Moses Sumney</v>
+        <v>Chris Young</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
       </c>
       <c r="L139" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>One Of Us - Chris Young</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Life On The Run</v>
+        <v>Sins of the Father</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-25</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Life On The Run - Single</v>
+        <v>Is God Is (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G140" t="str">
-        <v>3:49</v>
+        <v>3:20</v>
       </c>
       <c r="H140" t="str">
-        <v>Brandi Carlile</v>
+        <v>Moses Sumney</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
       </c>
       <c r="L140" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>Sins of the Father - Moses Sumney</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>New York Confident</v>
+        <v>Life On The Run</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-25</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>New York Confident - Single</v>
+        <v>Life On The Run - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:27</v>
+        <v>3:49</v>
       </c>
       <c r="H141" t="str">
-        <v>Mark Ambor</v>
+        <v>Brandi Carlile</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
       </c>
       <c r="L141" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>Life On The Run - Brandi Carlile</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>pequeñita!</v>
+        <v>New York Confident</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-25</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>pequeñita! - Single</v>
+        <v>New York Confident - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:39</v>
+        <v>2:27</v>
       </c>
       <c r="H142" t="str">
-        <v>Judeline</v>
+        <v>Mark Ambor</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
       </c>
       <c r="L142" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>New York Confident - Mark Ambor</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Opaline</v>
+        <v>pequeñita!</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-25</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>pequeñita! - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>3:17</v>
+        <v>2:39</v>
       </c>
       <c r="H143" t="str">
-        <v>Stephan Moccio</v>
+        <v>Judeline</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
       </c>
       <c r="L143" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>pequeñita! - Judeline</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pretty Little Things</v>
+        <v>Opaline</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-25</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G144" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H144" t="str">
-        <v>Lauv</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/opaline/1886736650</v>
       </c>
       <c r="L144" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>Opaline - Stephan Moccio</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>COLORADO</v>
+        <v>Pretty Little Things</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-25</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>COLORADO - Single</v>
+        <v>Pretty Little Things - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>1:54</v>
+        <v>2:51</v>
       </c>
       <c r="H145" t="str">
-        <v>Loud Luxury</v>
+        <v>Lauv</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
       </c>
       <c r="L145" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Infidelidad</v>
+        <v>COLORADO</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-25</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>El Disco de Salsa</v>
+        <v>COLORADO - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:29</v>
+        <v>1:54</v>
       </c>
       <c r="H146" t="str">
-        <v>Neutro Shorty</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/colorado/6769064981</v>
       </c>
       <c r="L146" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>COLORADO - Loud Luxury</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>Infidelidad</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-25</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Y'all Won</v>
+        <v>El Disco de Salsa</v>
       </c>
       <c r="G147" t="str">
-        <v>2:57</v>
+        <v>3:29</v>
       </c>
       <c r="H147" t="str">
-        <v>Veeze</v>
+        <v>Neutro Shorty</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
       </c>
       <c r="L147" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>Infidelidad - Neutro Shorty</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>La Semana</v>
+        <v>Wrong Place, Wrong time</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-25</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>Y'all Won</v>
       </c>
       <c r="G148" t="str">
-        <v>3:30</v>
+        <v>2:57</v>
       </c>
       <c r="H148" t="str">
-        <v>ELENA ROSE</v>
+        <v>Veeze</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
       </c>
       <c r="L148" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>Wrong Place, Wrong time - Veeze</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>La Semana</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-25</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Bandera Blanca</v>
+        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>3:34</v>
+        <v>3:30</v>
       </c>
       <c r="H149" t="str">
-        <v>Christian Nodal</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
       </c>
       <c r="L149" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>La Semana - ELENA ROSE</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Cold</v>
+        <v>Una Mujer Como la Suya</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-25</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Cold - Single</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G150" t="str">
-        <v>2:52</v>
+        <v>3:34</v>
       </c>
       <c r="H150" t="str">
-        <v>Majid Jordan</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
       </c>
       <c r="L150" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>Una Mujer Como la Suya - Christian Nodal</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>Cold</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-25</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>Cold - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:15</v>
+        <v>2:52</v>
       </c>
       <c r="H151" t="str">
-        <v>Ecca Vandal</v>
+        <v>Majid Jordan</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/cold/1895478371</v>
       </c>
       <c r="L151" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>Cold - Majid Jordan</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Child of Divorce</v>
+        <v>VERTICAL WORLDS</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-25</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>soft pop</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G152" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H152" t="str">
-        <v>Amy Shark</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
       </c>
       <c r="L152" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>VERTICAL WORLDS - Ecca Vandal</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Taboo</v>
+        <v>Child of Divorce</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-25</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Taboo - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G153" t="str">
-        <v>3:38</v>
+        <v>3:24</v>
       </c>
       <c r="H153" t="str">
-        <v>Jensen McRae</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
       </c>
       <c r="L153" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>Child of Divorce - Amy Shark</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>I'M OK</v>
+        <v>Taboo</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-25</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>A Rii Set</v>
+        <v>Taboo - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:37</v>
+        <v>3:38</v>
       </c>
       <c r="H154" t="str">
-        <v>Pheelz</v>
+        <v>Jensen McRae</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/taboo/1895036934</v>
       </c>
       <c r="L154" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>Taboo - Jensen McRae</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Butterfly Feelings</v>
+        <v>I'M OK</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-25</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Ritual</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G155" t="str">
-        <v>2:35</v>
+        <v>2:37</v>
       </c>
       <c r="H155" t="str">
-        <v>Icona Pop</v>
+        <v>Pheelz</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
       </c>
       <c r="L155" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>I'M OK - Pheelz</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>F**k the DJ</v>
+        <v>Butterfly Feelings</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-25</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>Ritual</v>
       </c>
       <c r="G156" t="str">
-        <v>2:57</v>
+        <v>2:35</v>
       </c>
       <c r="H156" t="str">
-        <v>Eli</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
       </c>
       <c r="L156" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>Butterfly Feelings - Icona Pop</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Grateful</v>
+        <v>F**k the DJ</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-25</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>24</v>
+        <v>Stage Girl (Not A Dream Anymore)</v>
       </c>
       <c r="G157" t="str">
-        <v>2:18</v>
+        <v>2:57</v>
       </c>
       <c r="H157" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Eli</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
       </c>
       <c r="L157" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>F**k the DJ - Eli</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Second Chance</v>
+        <v>Grateful</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-25</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Second Chance - Single</v>
+        <v>24</v>
       </c>
       <c r="G158" t="str">
-        <v>3:06</v>
+        <v>2:18</v>
       </c>
       <c r="H158" t="str">
-        <v>Lukas Graham</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/grateful/1887166427</v>
       </c>
       <c r="L158" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>Grateful - Alexis Ffrench</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>Second Chance</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-25</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>Second Chance - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>3:49</v>
+        <v>3:06</v>
       </c>
       <c r="H159" t="str">
-        <v>Tommy Lee</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
       </c>
       <c r="L159" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>Second Chance - Lukas Graham</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>DOOM LOOP</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-25</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>Tommyland Rides Again</v>
       </c>
       <c r="G160" t="str">
-        <v>4:00</v>
+        <v>3:49</v>
       </c>
       <c r="H160" t="str">
-        <v>PRESIDENT</v>
+        <v>Tommy Lee</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
       </c>
       <c r="L160" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>New York City</v>
+        <v>DOOM LOOP</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-25</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>New York City - Single</v>
+        <v>Blood Of Your Empire</v>
       </c>
       <c r="G161" t="str">
-        <v>3:30</v>
+        <v>4:00</v>
       </c>
       <c r="H161" t="str">
-        <v>Anthony Ramos</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
       </c>
       <c r="L161" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>DOOM LOOP - PRESIDENT</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>I Found You</v>
+        <v>New York City</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-25</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>I Found You - Single</v>
+        <v>New York City - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:18</v>
+        <v>3:30</v>
       </c>
       <c r="H162" t="str">
-        <v>TA Thomas</v>
+        <v>Anthony Ramos</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
       </c>
       <c r="L162" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>New York City - Anthony Ramos</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Just My Type</v>
+        <v>I Found You</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-25</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Labor Of Love</v>
+        <v>I Found You - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:40</v>
+        <v>3:18</v>
       </c>
       <c r="H163" t="str">
-        <v>Blxst</v>
+        <v>TA Thomas</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
       </c>
       <c r="L163" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>I Found You - TA Thomas</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>teenage drama</v>
+        <v>Just My Type</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-25</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>teenage drama - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G164" t="str">
-        <v>3:06</v>
+        <v>2:40</v>
       </c>
       <c r="H164" t="str">
-        <v>paris jackson</v>
+        <v>Blxst</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
       </c>
       <c r="L164" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>Just My Type - Blxst</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>does it still mean something?</v>
+        <v>teenage drama</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-25</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>only if it matters</v>
+        <v>teenage drama - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:48</v>
+        <v>3:06</v>
       </c>
       <c r="H165" t="str">
-        <v>Kevian Kraemer</v>
+        <v>paris jackson</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
       </c>
       <c r="L165" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>teenage drama - paris jackson</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>does it still mean something?</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-25</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>only if it matters</v>
       </c>
       <c r="G166" t="str">
-        <v>3:00</v>
+        <v>3:48</v>
       </c>
       <c r="H166" t="str">
-        <v>Ruel</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
       </c>
       <c r="L166" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>does it still mean something? - Kevian Kraemer</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>Debbie Don't Cry</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-25</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>Debbie Don't Cry - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H167" t="str">
-        <v>Cruz Beckham</v>
+        <v>Ruel</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
       </c>
       <c r="L167" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>Debbie Don't Cry - Ruel</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Cotton Flower</v>
+        <v>YEAH YEAH YEAH</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-25</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>YEAH YEAH YEAH - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:53</v>
+        <v>2:25</v>
       </c>
       <c r="H168" t="str">
-        <v>Future Islands</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
       </c>
       <c r="L168" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>YEAH YEAH YEAH - Cruz Beckham</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>Cotton Flower</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-25</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G169" t="str">
-        <v>3:22</v>
+        <v>3:53</v>
       </c>
       <c r="H169" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Future Islands</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
       </c>
       <c r="L169" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>Cotton Flower - Future Islands</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Comfort</v>
+        <v>WAHALA RIDDIM</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-25</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>So Help Me God</v>
+        <v>WAHALA RIDDIM - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>5:35</v>
+        <v>3:22</v>
       </c>
       <c r="H170" t="str">
-        <v>Kelsey Lu</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
       </c>
       <c r="L170" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>WAHALA RIDDIM - THEHONESTGUY</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Skin</v>
+        <v>Comfort</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-25</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Skin - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G171" t="str">
-        <v>3:00</v>
+        <v>5:35</v>
       </c>
       <c r="H171" t="str">
-        <v>Alessi Rose</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/comfort/1876521144</v>
       </c>
       <c r="L171" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>Comfort - Kelsey Lu</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>IDGAF</v>
+        <v>Skin</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-25</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>IDGAF - Single</v>
+        <v>Skin - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:55</v>
+        <v>3:00</v>
       </c>
       <c r="H172" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Alessi Rose</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/skin/1895865252</v>
       </c>
       <c r="L172" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>Skin - Alessi Rose</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Run Rabbit</v>
+        <v>IDGAF</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-25</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>IDGAF - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:09</v>
+        <v>2:55</v>
       </c>
       <c r="H173" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
       </c>
       <c r="L173" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>IDGAF - Katelyn Tarver</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>Run Rabbit</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-25</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>Run Rabbit - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:03</v>
+        <v>3:09</v>
       </c>
       <c r="H174" t="str">
-        <v>CamelPhat</v>
+        <v>Mollie Elizabeth</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
       </c>
       <c r="L174" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>Run Rabbit - Mollie Elizabeth</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>So Good (feat. Kuuda)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-25</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>So Good (feat. Kuuda) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>5:01</v>
+        <v>3:03</v>
       </c>
       <c r="H175" t="str">
-        <v>Lane 8</v>
+        <v>CamelPhat</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
       </c>
       <c r="L175" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>So Good (feat. Kuuda) - CamelPhat</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>regalametutiempo</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-25</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>PROYECTANDO</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="G176" t="str">
-        <v>3:01</v>
+        <v>5:01</v>
       </c>
       <c r="H176" t="str">
-        <v>Julio Caesar</v>
+        <v>Lane 8</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
       </c>
       <c r="L176" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>Empty Theatre, Pretty Picture - Lane 8</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>On Sight</v>
+        <v>regalametutiempo</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-25</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Left on RED</v>
+        <v>PROYECTANDO</v>
       </c>
       <c r="G177" t="str">
-        <v>2:25</v>
+        <v>3:01</v>
       </c>
       <c r="H177" t="str">
-        <v>REMI</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
       </c>
       <c r="L177" t="str">
-        <v>On Sight - REMI</v>
+        <v>regalametutiempo - Julio Caesar</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Masks Off</v>
+        <v>On Sight</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-25</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Masks Off - Single</v>
+        <v>Left on RED</v>
       </c>
       <c r="G178" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H178" t="str">
-        <v>Jesse Welles</v>
+        <v>REMI</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/remi/1716510008</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
       </c>
       <c r="L178" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>On Sight - REMI</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>I'm Just A Girl</v>
+        <v>Masks Off</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-25</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>Masks Off - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H179" t="str">
-        <v>Thee Marloes</v>
+        <v>Jesse Welles</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
       </c>
       <c r="L179" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>Masks Off - Jesse Welles</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>I'm Just A Girl</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-25</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>EXIT 2B</v>
+        <v>Di Hotel Malibu</v>
       </c>
       <c r="G180" t="str">
-        <v>2:11</v>
+        <v>2:49</v>
       </c>
       <c r="H180" t="str">
-        <v>B0YG1RL</v>
+        <v>Thee Marloes</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
       </c>
       <c r="L180" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>I'm Just A Girl - Thee Marloes</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Money Tree</v>
+        <v>Soleil (feat. Isabella Lovestory)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-25</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Money Tree - Single</v>
+        <v>EXIT 2B</v>
       </c>
       <c r="G181" t="str">
-        <v>2:39</v>
+        <v>2:11</v>
       </c>
       <c r="H181" t="str">
-        <v>Olympia Vitalis</v>
+        <v>B0YG1RL</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
       </c>
       <c r="L181" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Homerunner</v>
+        <v>Money Tree</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-25</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Homerunner - Single</v>
+        <v>Money Tree - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H182" t="str">
-        <v>slayr</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
       </c>
       <c r="L182" t="str">
-        <v>Homerunner - slayr</v>
+        <v>Money Tree - Olympia Vitalis</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Mail</v>
+        <v>Homerunner</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
+        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-25</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Mail - Single</v>
+        <v>Homerunner - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:14</v>
+        <v>2:36</v>
       </c>
       <c r="H183" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
+        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
       </c>
       <c r="L183" t="str">
-        <v>Mail - MexikoDro</v>
+        <v>Homerunner - slayr</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Waste Your Heart</v>
+        <v>Mail</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
+        <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-25</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Waste Your Heart - Single</v>
+        <v>Mail - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:31</v>
+        <v>2:14</v>
       </c>
       <c r="H184" t="str">
-        <v>Magnus Ferrell</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
+        <v>https://music.apple.com/us/album/mail/6769190634</v>
       </c>
       <c r="L184" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
+        <v>Mail - MexikoDro</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Sleeping Pills</v>
+        <v>Waste Your Heart</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
+        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-25</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Sleeping Pills - Single</v>
+        <v>Waste Your Heart - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:03</v>
+        <v>2:31</v>
       </c>
       <c r="H185" t="str">
-        <v>Dolder</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
+        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
       </c>
       <c r="L185" t="str">
-        <v>Sleeping Pills - Dolder</v>
+        <v>Waste Your Heart - Magnus Ferrell</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>KODACHROMATIC</v>
+        <v>Sleeping Pills</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
+        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-25</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>KODACHROMATIC - Single</v>
+        <v>Sleeping Pills - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:53</v>
+        <v>3:03</v>
       </c>
       <c r="H186" t="str">
-        <v>Tiger La Flor</v>
+        <v>Dolder</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
+        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
       </c>
       <c r="L186" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
+        <v>Sleeping Pills - Dolder</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>FOMO</v>
+        <v>KODACHROMATIC</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
+        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-25</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Map Of Her Shadow</v>
+        <v>KODACHROMATIC - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:01</v>
+        <v>2:53</v>
       </c>
       <c r="H187" t="str">
-        <v>Anais Cardot</v>
+        <v>Tiger La Flor</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
+        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
       </c>
       <c r="L187" t="str">
-        <v>FOMO - Anais Cardot</v>
+        <v>KODACHROMATIC - Tiger La Flor</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Black Fire</v>
+        <v>FOMO</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
+        <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-25</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Sulfur Surfer</v>
+        <v>Map Of Her Shadow</v>
       </c>
       <c r="G188" t="str">
-        <v>3:37</v>
+        <v>3:01</v>
       </c>
       <c r="H188" t="str">
-        <v>Bladee</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
+        <v>https://music.apple.com/us/album/fomo/1890190623</v>
       </c>
       <c r="L188" t="str">
-        <v>Black Fire - Bladee</v>
+        <v>FOMO - Anais Cardot</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>As Seen in the Unseen</v>
+        <v>Black Fire</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
+        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-25</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Sulfur Surfer</v>
       </c>
       <c r="G189" t="str">
-        <v>6:59</v>
+        <v>3:37</v>
       </c>
       <c r="H189" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Bladee</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/bladee/861359576</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
+        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
       </c>
       <c r="L189" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
+        <v>Black Fire - Bladee</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Every Man-Any Man</v>
+        <v>As Seen in the Unseen</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
+        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-25</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G190" t="str">
-        <v>4:20</v>
+        <v>6:59</v>
       </c>
       <c r="H190" t="str">
-        <v>Armored Saint</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
+        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
       </c>
       <c r="L190" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
+        <v>As Seen in the Unseen - Dimmu Borgir</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>No Arms</v>
+        <v>Every Man-Any Man</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
+        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-25</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>From A Distance</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G191" t="str">
-        <v>3:43</v>
+        <v>4:20</v>
       </c>
       <c r="H191" t="str">
-        <v>156/Silence</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
+        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
       </c>
       <c r="L191" t="str">
-        <v>No Arms - 156/Silence</v>
+        <v>Every Man-Any Man - Armored Saint</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>It's Neverending</v>
+        <v>No Arms</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
+        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-25</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Neverending</v>
+        <v>From A Distance</v>
       </c>
       <c r="G192" t="str">
-        <v>8:35</v>
+        <v>3:43</v>
       </c>
       <c r="H192" t="str">
-        <v>Monolord</v>
+        <v>156/Silence</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
+        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
       </c>
       <c r="L192" t="str">
-        <v>It's Neverending - Monolord</v>
+        <v>No Arms - 156/Silence</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>The Kids Will Kill Us</v>
+        <v>It's Neverending</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
+        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-25</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>The Kids Will Kill Us - Single</v>
+        <v>Neverending</v>
       </c>
       <c r="G193" t="str">
-        <v>3:45</v>
+        <v>8:35</v>
       </c>
       <c r="H193" t="str">
-        <v>Witch Club Satan</v>
+        <v>Monolord</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
+        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
       </c>
       <c r="L193" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
+        <v>It's Neverending - Monolord</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
+        <v>The Kids Will Kill Us</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
+        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-25</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
+        <v>The Kids Will Kill Us - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:20</v>
+        <v>3:45</v>
       </c>
       <c r="H194" t="str">
-        <v>The Darkness</v>
+        <v>Witch Club Satan</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
+        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
+        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
       </c>
       <c r="L194" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
+        <v>The Kids Will Kill Us - Witch Club Satan</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>All Day</v>
+        <v>Masters of the Universe (from "Masters of the Universe")</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
+        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-25</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Feet On Fire</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:29</v>
+        <v>3:20</v>
       </c>
       <c r="H195" t="str">
-        <v>Ben Chapman</v>
+        <v>The Darkness</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
+        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
+        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
       </c>
       <c r="L195" t="str">
-        <v>All Day - Ben Chapman</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Sigui</v>
+        <v>All Day</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
+        <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-25</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Massa</v>
+        <v>Feet On Fire</v>
       </c>
       <c r="G196" t="str">
-        <v>3:17</v>
+        <v>2:29</v>
       </c>
       <c r="H196" t="str">
-        <v>Fatoumata Diawara</v>
+        <v>Ben Chapman</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
+        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
+        <v>https://music.apple.com/us/album/all-day/1880746349</v>
       </c>
       <c r="L196" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
+        <v>All Day - Ben Chapman</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>High Tail</v>
+        <v>Sigui</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
+        <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-25</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Where the South Winds Wail</v>
+        <v>Massa</v>
       </c>
       <c r="G197" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H197" t="str">
-        <v>Gitkin</v>
+        <v>Fatoumata Diawara</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
+        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
+        <v>https://music.apple.com/us/album/sigui/1890241617</v>
       </c>
       <c r="L197" t="str">
-        <v>High Tail - Gitkin</v>
+        <v>Sigui - Fatoumata Diawara</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Mice Protection</v>
+        <v>High Tail</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-25</v>
@@ -7899,68 +7899,106 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Ugly Duckling Union</v>
+        <v>Where the South Winds Wail</v>
       </c>
       <c r="G198" t="str">
-        <v>3:34</v>
+        <v>2:31</v>
       </c>
       <c r="H198" t="str">
-        <v>Lowertown</v>
+        <v>Gitkin</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
       </c>
       <c r="L198" t="str">
-        <v>Mice Protection - Lowertown</v>
+        <v>High Tail - Gitkin</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
+        <v>Mice Protection</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Ugly Duckling Union</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:34</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Lowertown</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Mice Protection - Lowertown</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Tóxica</v>
       </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
-      <c r="D199" t="str">
-        <v>2026-05-25</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
+      <c r="D200" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
         <v>Caribenya</v>
       </c>
-      <c r="G199" t="str">
+      <c r="G200" t="str">
         <v>3:48</v>
       </c>
-      <c r="H199" t="str">
+      <c r="H200" t="str">
         <v>Lido Pimienta</v>
       </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
         <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
       </c>
-      <c r="K199" t="str">
+      <c r="K200" t="str">
         <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
       </c>
-      <c r="L199" t="str">
+      <c r="L200" t="str">
         <v>Tóxica - Lido Pimienta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B57" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B85" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B86" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B88" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B96" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B97" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B98" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B3" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B4" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B5" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B6" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B10" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B11" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B12" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B13" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B17" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B19" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B21" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B25" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B29" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B31" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B33" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B35" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B36" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B38" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B42" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B43" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B45" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B47" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B48" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B49" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B53" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B57" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B60" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B76" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B78" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B80" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B85" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B86" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B88" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B89" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B91" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B92" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B96" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B97" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B98" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-26</v>
       </c>
       <c r="E200" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B5" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -1655,7 +1655,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B86" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -875,7 +875,7 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Brandon Lake</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,7 +887,7 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="14">
@@ -1617,7 +1617,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B44" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B62" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B65" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3669,19 +3669,19 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-27</v>
       </c>
       <c r="E200" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>20h ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-27</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>20h ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>14h ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-27</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>14h ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Lainey Wilson</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-27</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Duran Duran</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B5" t="str">
-        <v>6 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-27</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 days ago</v>
+        <v>1d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Nico Santos</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-27</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-27</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Will Linley</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-27</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Kylie Minogue</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-27</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Billy Raffoul</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-27</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>The Offspring</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-27</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>David Gilmour</v>
+        <v>Will Linley</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-27</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Scorpions</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-27</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-27</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>The Offspring</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-27</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>The Warning</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-27</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>paris jackson</v>
+        <v>Scorpions</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-27</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Minelli</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-27</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Maggie Rose</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-27</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>David Guetta</v>
+        <v>The Warning</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-27</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>paris jackson</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-27</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Lauv</v>
+        <v>Minelli</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-27</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Icona Pop</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-27</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>Will Swinton</v>
+        <v>David Guetta</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-27</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Dean Lewis</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-27</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Lauv</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-27</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Niall Horan</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-27</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-27</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>RUEL</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-27</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>TINI</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-27</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Charli xcx</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-27</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Dua Lipa</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-27</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Matilda Mann</v>
+        <v>RUEL</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B33" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-27</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Ella Langley</v>
+        <v>TINI</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-27</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B35" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-27</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>6 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>kesha</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-27</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Holly Humberstone</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-27</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Foo Fighters</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-27</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>The Analogues</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-27</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Rod Stewart</v>
+        <v>kesha</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-27</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Blue October</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-27</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Far Caspian</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-27</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Kenia Os</v>
+        <v>The Analogues</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-27</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-27</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Blue October</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-27</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B46" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-27</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B47" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-27</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>10 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-27</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-27</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-27</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Evanescence</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-27</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-27</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Armin van Buuren</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B53" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-27</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Madison Cunningham</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-27</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Johnny Orlando</v>
+        <v>Evanescence</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>11 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-27</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>11 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Carver Jones</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B56" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-27</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Jazmin bean</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B57" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-27</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>11 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Baby Queen</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-27</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Switchfoot</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-27</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Grace Potter</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-27</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-27</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>The All-American Rejects</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-27</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Henry Moodie</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-27</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Spacey Jane</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-27</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Megan Moroney</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-27</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Matt Hansen</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-27</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Matt Hansen</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-27</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Keith Urban</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-27</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>VALÉ</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-27</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-27</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Towa Bird</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-27</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-27</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Little Big Town</v>
+        <v>VALÉ</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-27</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Becky G</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-27</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Daisy the Great</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-27</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Towa Bird</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-27</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Madonna</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-27</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Ally Salort</v>
+        <v>Becky G</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-27</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Bella White</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-27</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-27</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Towa Bird</v>
+        <v>Madonna</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-27</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Miranda Lambert</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-27</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Lady Gaga</v>
+        <v>Bella White</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-27</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Gracie Abrams</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-27</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-27</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Martin Garrix</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-27</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Jorja Smith</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-27</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>LP</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-27</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>The Rolling Stones</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-27</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Oasis</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-27</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-27</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>VictorBiliac</v>
+        <v>LP</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-27</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Linkin Park</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-27</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Harry Styles</v>
+        <v>Oasis</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-27</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Eagles</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-27</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>Nora Fatehi</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B96" t="str">
-        <v>2 months ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-27</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 months ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Linkin Park</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2 months ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-27</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 months ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 months ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-27</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 months ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Eagles</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video)</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-27</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>The Head And The Heart</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-27</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Simply Red</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video)</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-27</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Talking Heads</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B2" t="str">
-        <v>20h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20h ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B3" t="str">
-        <v>14h ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>14h ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B7" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B8" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B9" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B10" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B14" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B15" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B16" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B17" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B20" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B21" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B23" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B25" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B26" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B29" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B33" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B35" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B37" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B39" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B40" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B42" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B43" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B46" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B47" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B48" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B49" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B50" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B51" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B52" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B53" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B56" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B57" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B60" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B61" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B62" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B63" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B64" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B66" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B69" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B70" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B71" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B73" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B78" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B80" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B82" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B84" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B85" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B86" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B89" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B90" t="str">
-        <v>12d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>12d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B91" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B92" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B93" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>From The Inside (Live in Mumbai) - Linkin Park</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B100" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B101" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>STOP</v>
+        <v>The Wave</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-27</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Sunshine</v>
       </c>
       <c r="G102" t="str">
-        <v>2:56</v>
+        <v>3:22</v>
       </c>
       <c r="H102" t="str">
-        <v>Bella Kay</v>
+        <v>Jungle</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L102" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="103">
@@ -4502,13 +4502,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>we should talk</v>
+        <v>STOP</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-27</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>everyone for ten minutes</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G109" t="str">
-        <v>3:04</v>
+        <v>2:56</v>
       </c>
       <c r="H109" t="str">
-        <v>Bleachers</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L109" t="str">
-        <v>we should talk - Bleachers</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Do What You Gotta Do</v>
+        <v>we should talk</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
+        <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-27</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>everyone for ten minutes</v>
       </c>
       <c r="G110" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H110" t="str">
-        <v>The Band CAMINO</v>
+        <v>Bleachers</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/bleachers/824434533</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
+        <v>https://music.apple.com/us/album/we-should-talk/1872842313</v>
       </c>
       <c r="L110" t="str">
-        <v>Do What You Gotta Do - The Band CAMINO</v>
+        <v>we should talk - Bleachers</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Ego</v>
+        <v>Do What You Gotta Do</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-27</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Ego - Single</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G111" t="str">
-        <v>2:53</v>
+        <v>3:26</v>
       </c>
       <c r="H111" t="str">
-        <v>The Warning</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/do-what-you-gotta-do/1887616173</v>
       </c>
       <c r="L111" t="str">
-        <v>Ego - The Warning</v>
+        <v>Do What You Gotta Do - The Band CAMINO</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>Ego</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-27</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H112" t="str">
-        <v>Kylie Minogue</v>
+        <v>The Warning</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L112" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>All That Matters</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-27</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:43</v>
+        <v>3:17</v>
       </c>
       <c r="H113" t="str">
-        <v>6LACK</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L113" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Like A Virgin</v>
+        <v>All That Matters</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-27</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Terrified .</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G114" t="str">
-        <v>2:34</v>
+        <v>3:43</v>
       </c>
       <c r="H114" t="str">
-        <v>fakemink</v>
+        <v>6LACK</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L114" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>24 Hours</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-27</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>24 Hours - Single</v>
+        <v>Terrified .</v>
       </c>
       <c r="G115" t="str">
-        <v>3:17</v>
+        <v>2:34</v>
       </c>
       <c r="H115" t="str">
-        <v>Stormzy</v>
+        <v>fakemink</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L115" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>24 Hours</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-27</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:09</v>
+        <v>3:17</v>
       </c>
       <c r="H116" t="str">
-        <v>Lizzo</v>
+        <v>Stormzy</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L116" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Ms. Tundra</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-27</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Highway 79</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:12</v>
+        <v>2:09</v>
       </c>
       <c r="H117" t="str">
-        <v>Ne-Yo</v>
+        <v>Lizzo</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L117" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>TARENTINO</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-27</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>TARENTINO - Single</v>
+        <v>Highway 79</v>
       </c>
       <c r="G118" t="str">
-        <v>2:23</v>
+        <v>3:12</v>
       </c>
       <c r="H118" t="str">
-        <v>Labrinth</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L118" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Daydreamin’</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-27</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>2:58</v>
+        <v>2:23</v>
       </c>
       <c r="H119" t="str">
-        <v>ZAYN</v>
+        <v>Labrinth</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L119" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>End of an Era</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-27</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Dinner Party</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G120" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H120" t="str">
-        <v>Niall Horan</v>
+        <v>ZAYN</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L120" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Questions</v>
+        <v>End of an Era</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-27</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Florescence</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G121" t="str">
-        <v>3:07</v>
+        <v>3:38</v>
       </c>
       <c r="H121" t="str">
-        <v>Maisie Peters</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L121" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Questions</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-27</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G122" t="str">
-        <v>3:12</v>
+        <v>3:07</v>
       </c>
       <c r="H122" t="str">
-        <v>Blondshell</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L122" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-27</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:44</v>
+        <v>3:12</v>
       </c>
       <c r="H123" t="str">
-        <v>Kygo</v>
+        <v>Blondshell</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
       </c>
       <c r="L123" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>Heart Has To Work So Hard - Blondshell</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-27</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>OMAKASE</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>4:03</v>
+        <v>3:44</v>
       </c>
       <c r="H124" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Kygo</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
       </c>
       <c r="L124" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Dosis</v>
+        <v>PERDISTE EL EMMY.</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-27</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>DOSIS</v>
+        <v>OMAKASE</v>
       </c>
       <c r="G125" t="str">
-        <v>3:00</v>
+        <v>4:03</v>
       </c>
       <c r="H125" t="str">
-        <v>Xavi</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
       </c>
       <c r="L125" t="str">
-        <v>Dosis - Xavi</v>
+        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Would U Still Love Me</v>
+        <v>Dosis</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-27</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>DOSIS</v>
       </c>
       <c r="G126" t="str">
-        <v>2:36</v>
+        <v>3:00</v>
       </c>
       <c r="H126" t="str">
-        <v>Diplo</v>
+        <v>Xavi</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/dosis/1895081885</v>
       </c>
       <c r="L126" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>Dosis - Xavi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Saving This Bottle</v>
+        <v>Would U Still Love Me</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-27</v>
@@ -5204,7 +5204,7 @@
         <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>3:05</v>
+        <v>2:36</v>
       </c>
       <c r="H127" t="str">
         <v>Diplo</v>
@@ -5216,21 +5216,21 @@
         <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
       </c>
       <c r="L127" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>Would U Still Love Me - Diplo</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>The Climb</v>
+        <v>Saving This Bottle</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-27</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>The Climb - Single</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:50</v>
+        <v>3:05</v>
       </c>
       <c r="H128" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Diplo</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
       </c>
       <c r="L128" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>Saving This Bottle - Diplo</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>everything tatted</v>
+        <v>The Climb</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-27</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>everything tatted - Single</v>
+        <v>The Climb - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:25</v>
+        <v>3:50</v>
       </c>
       <c r="H129" t="str">
-        <v>mgk</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
       </c>
       <c r="L129" t="str">
-        <v>everything tatted - mgk</v>
+        <v>The Climb - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>BOOMPALA</v>
+        <v>everything tatted</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-27</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>everything tatted - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:56</v>
+        <v>3:25</v>
       </c>
       <c r="H130" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
       </c>
       <c r="L130" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>everything tatted - mgk</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>BOOMPALA</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-27</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>can we do it all again?</v>
+        <v>'PUREFLOW', Pt. 1</v>
       </c>
       <c r="G131" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H131" t="str">
-        <v>Sonny Fodera</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/boompala/1894802719</v>
       </c>
       <c r="L131" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>BOOMPALA - LE SSERAFIM</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>Let Me Be In Your Arms</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-27</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>can we do it all again?</v>
       </c>
       <c r="G132" t="str">
-        <v>2:28</v>
+        <v>3:13</v>
       </c>
       <c r="H132" t="str">
-        <v>Sheff G</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
       </c>
       <c r="L132" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>Let Me Be In Your Arms - Sonny Fodera</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>touch myself</v>
+        <v>Eat, Work, Pray</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-27</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>and all pride aside</v>
+        <v>Eat, Work, Pray - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>4:09</v>
+        <v>2:28</v>
       </c>
       <c r="H133" t="str">
-        <v>kwn</v>
+        <v>Sheff G</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
       </c>
       <c r="L133" t="str">
-        <v>touch myself - kwn</v>
+        <v>Eat, Work, Pray - Sheff G</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Comes and Goes</v>
+        <v>touch myself</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-27</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>and all pride aside</v>
       </c>
       <c r="G134" t="str">
-        <v>4:22</v>
+        <v>4:09</v>
       </c>
       <c r="H134" t="str">
-        <v>KETTAMA</v>
+        <v>kwn</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
       </c>
       <c r="L134" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>touch myself - kwn</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Dear God</v>
+        <v>Comes and Goes</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-27</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Dear God</v>
+        <v>Comes and Goes - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>6:08</v>
+        <v>4:22</v>
       </c>
       <c r="H135" t="str">
-        <v>The Pretty Reckless</v>
+        <v>KETTAMA</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
       </c>
       <c r="L135" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>Comes and Goes - KETTAMA</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Hexagons</v>
+        <v>Dear God</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-27</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>The Wow! Signal</v>
+        <v>Dear God</v>
       </c>
       <c r="G136" t="str">
-        <v>5:26</v>
+        <v>6:08</v>
       </c>
       <c r="H136" t="str">
-        <v>Muse</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
       </c>
       <c r="L136" t="str">
-        <v>Hexagons - Muse</v>
+        <v>Dear God - The Pretty Reckless</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Facile-Batiste</v>
+        <v>Hexagons</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-27</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Black Mozart</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G137" t="str">
-        <v>4:55</v>
+        <v>5:26</v>
       </c>
       <c r="H137" t="str">
-        <v>Jon Batiste</v>
+        <v>Muse</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
       </c>
       <c r="L137" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Hexagons - Muse</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Pop Pop</v>
+        <v>Facile-Batiste</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-27</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Pop Pop - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G138" t="str">
-        <v>2:57</v>
+        <v>4:55</v>
       </c>
       <c r="H138" t="str">
-        <v>Channel Tres</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
       </c>
       <c r="L138" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>Facile-Batiste - Jon Batiste</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>One Of Us</v>
+        <v>Pop Pop</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-27</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>One Of Us - Single</v>
+        <v>Pop Pop - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:35</v>
+        <v>2:57</v>
       </c>
       <c r="H139" t="str">
-        <v>Chris Young</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
       </c>
       <c r="L139" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>Pop Pop - Channel Tres</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Sins of the Father</v>
+        <v>One Of Us</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-27</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>One Of Us - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:20</v>
+        <v>3:35</v>
       </c>
       <c r="H140" t="str">
-        <v>Moses Sumney</v>
+        <v>Chris Young</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
       </c>
       <c r="L140" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>One Of Us - Chris Young</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Life On The Run</v>
+        <v>Sins of the Father</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-27</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Life On The Run - Single</v>
+        <v>Is God Is (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G141" t="str">
-        <v>3:49</v>
+        <v>3:20</v>
       </c>
       <c r="H141" t="str">
-        <v>Brandi Carlile</v>
+        <v>Moses Sumney</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
       </c>
       <c r="L141" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>Sins of the Father - Moses Sumney</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>New York Confident</v>
+        <v>Life On The Run</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-27</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>New York Confident - Single</v>
+        <v>Life On The Run - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:27</v>
+        <v>3:49</v>
       </c>
       <c r="H142" t="str">
-        <v>Mark Ambor</v>
+        <v>Brandi Carlile</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
       </c>
       <c r="L142" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>Life On The Run - Brandi Carlile</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>pequeñita!</v>
+        <v>New York Confident</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-27</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>pequeñita! - Single</v>
+        <v>New York Confident - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:39</v>
+        <v>2:27</v>
       </c>
       <c r="H143" t="str">
-        <v>Judeline</v>
+        <v>Mark Ambor</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
       </c>
       <c r="L143" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>New York Confident - Mark Ambor</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Opaline</v>
+        <v>pequeñita!</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-27</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>pequeñita! - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:17</v>
+        <v>2:39</v>
       </c>
       <c r="H144" t="str">
-        <v>Stephan Moccio</v>
+        <v>Judeline</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
       </c>
       <c r="L144" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>pequeñita! - Judeline</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pretty Little Things</v>
+        <v>Opaline</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-27</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G145" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H145" t="str">
-        <v>Lauv</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/opaline/1886736650</v>
       </c>
       <c r="L145" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>Opaline - Stephan Moccio</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>COLORADO</v>
+        <v>Pretty Little Things</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-27</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>COLORADO - Single</v>
+        <v>Pretty Little Things - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>1:54</v>
+        <v>2:51</v>
       </c>
       <c r="H146" t="str">
-        <v>Loud Luxury</v>
+        <v>Lauv</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
       </c>
       <c r="L146" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Infidelidad</v>
+        <v>COLORADO</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-27</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>El Disco de Salsa</v>
+        <v>COLORADO - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:29</v>
+        <v>1:54</v>
       </c>
       <c r="H147" t="str">
-        <v>Neutro Shorty</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/colorado/6769064981</v>
       </c>
       <c r="L147" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>COLORADO - Loud Luxury</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>Infidelidad</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-27</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Y'all Won</v>
+        <v>El Disco de Salsa</v>
       </c>
       <c r="G148" t="str">
-        <v>2:57</v>
+        <v>3:29</v>
       </c>
       <c r="H148" t="str">
-        <v>Veeze</v>
+        <v>Neutro Shorty</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
       </c>
       <c r="L148" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>Infidelidad - Neutro Shorty</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>La Semana</v>
+        <v>Wrong Place, Wrong time</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-27</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>Y'all Won</v>
       </c>
       <c r="G149" t="str">
-        <v>3:30</v>
+        <v>2:57</v>
       </c>
       <c r="H149" t="str">
-        <v>ELENA ROSE</v>
+        <v>Veeze</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
       </c>
       <c r="L149" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>Wrong Place, Wrong time - Veeze</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>La Semana</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-27</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Bandera Blanca</v>
+        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
       </c>
       <c r="G150" t="str">
-        <v>3:34</v>
+        <v>3:30</v>
       </c>
       <c r="H150" t="str">
-        <v>Christian Nodal</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
       </c>
       <c r="L150" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>La Semana - ELENA ROSE</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Cold</v>
+        <v>Una Mujer Como la Suya</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-27</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Cold - Single</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G151" t="str">
-        <v>2:52</v>
+        <v>3:34</v>
       </c>
       <c r="H151" t="str">
-        <v>Majid Jordan</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
       </c>
       <c r="L151" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>Una Mujer Como la Suya - Christian Nodal</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>Cold</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-27</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>Cold - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:15</v>
+        <v>2:52</v>
       </c>
       <c r="H152" t="str">
-        <v>Ecca Vandal</v>
+        <v>Majid Jordan</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/cold/1895478371</v>
       </c>
       <c r="L152" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>Cold - Majid Jordan</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Child of Divorce</v>
+        <v>VERTICAL WORLDS</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-27</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>soft pop</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G153" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H153" t="str">
-        <v>Amy Shark</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
       </c>
       <c r="L153" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>VERTICAL WORLDS - Ecca Vandal</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Taboo</v>
+        <v>Child of Divorce</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-27</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Taboo - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G154" t="str">
-        <v>3:38</v>
+        <v>3:24</v>
       </c>
       <c r="H154" t="str">
-        <v>Jensen McRae</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
       </c>
       <c r="L154" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>Child of Divorce - Amy Shark</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>I'M OK</v>
+        <v>Taboo</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-27</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>A Rii Set</v>
+        <v>Taboo - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>2:37</v>
+        <v>3:38</v>
       </c>
       <c r="H155" t="str">
-        <v>Pheelz</v>
+        <v>Jensen McRae</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/taboo/1895036934</v>
       </c>
       <c r="L155" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>Taboo - Jensen McRae</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Butterfly Feelings</v>
+        <v>I'M OK</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-27</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Ritual</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G156" t="str">
-        <v>2:35</v>
+        <v>2:37</v>
       </c>
       <c r="H156" t="str">
-        <v>Icona Pop</v>
+        <v>Pheelz</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
       </c>
       <c r="L156" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>I'M OK - Pheelz</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>F**k the DJ</v>
+        <v>Butterfly Feelings</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-27</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>Ritual</v>
       </c>
       <c r="G157" t="str">
-        <v>2:57</v>
+        <v>2:35</v>
       </c>
       <c r="H157" t="str">
-        <v>Eli</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
       </c>
       <c r="L157" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>Butterfly Feelings - Icona Pop</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Grateful</v>
+        <v>F**k the DJ</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-27</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>24</v>
+        <v>Stage Girl (Not A Dream Anymore)</v>
       </c>
       <c r="G158" t="str">
-        <v>2:18</v>
+        <v>2:57</v>
       </c>
       <c r="H158" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Eli</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
       </c>
       <c r="L158" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>F**k the DJ - Eli</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Second Chance</v>
+        <v>Grateful</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-27</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Second Chance - Single</v>
+        <v>24</v>
       </c>
       <c r="G159" t="str">
-        <v>3:06</v>
+        <v>2:18</v>
       </c>
       <c r="H159" t="str">
-        <v>Lukas Graham</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/grateful/1887166427</v>
       </c>
       <c r="L159" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>Grateful - Alexis Ffrench</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>Second Chance</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-27</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>Second Chance - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:49</v>
+        <v>3:06</v>
       </c>
       <c r="H160" t="str">
-        <v>Tommy Lee</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
       </c>
       <c r="L160" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>Second Chance - Lukas Graham</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>DOOM LOOP</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-27</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>Tommyland Rides Again</v>
       </c>
       <c r="G161" t="str">
-        <v>4:00</v>
+        <v>3:49</v>
       </c>
       <c r="H161" t="str">
-        <v>PRESIDENT</v>
+        <v>Tommy Lee</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
       </c>
       <c r="L161" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>New York City</v>
+        <v>DOOM LOOP</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-27</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>New York City - Single</v>
+        <v>Blood Of Your Empire</v>
       </c>
       <c r="G162" t="str">
-        <v>3:30</v>
+        <v>4:00</v>
       </c>
       <c r="H162" t="str">
-        <v>Anthony Ramos</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
       </c>
       <c r="L162" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>DOOM LOOP - PRESIDENT</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>I Found You</v>
+        <v>New York City</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-27</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>I Found You - Single</v>
+        <v>New York City - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:18</v>
+        <v>3:30</v>
       </c>
       <c r="H163" t="str">
-        <v>TA Thomas</v>
+        <v>Anthony Ramos</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
       </c>
       <c r="L163" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>New York City - Anthony Ramos</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Just My Type</v>
+        <v>I Found You</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-27</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Labor Of Love</v>
+        <v>I Found You - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:40</v>
+        <v>3:18</v>
       </c>
       <c r="H164" t="str">
-        <v>Blxst</v>
+        <v>TA Thomas</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
       </c>
       <c r="L164" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>I Found You - TA Thomas</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>teenage drama</v>
+        <v>Just My Type</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-27</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>teenage drama - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G165" t="str">
-        <v>3:06</v>
+        <v>2:40</v>
       </c>
       <c r="H165" t="str">
-        <v>paris jackson</v>
+        <v>Blxst</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
       </c>
       <c r="L165" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>Just My Type - Blxst</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>does it still mean something?</v>
+        <v>teenage drama</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-27</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>only if it matters</v>
+        <v>teenage drama - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>3:48</v>
+        <v>3:06</v>
       </c>
       <c r="H166" t="str">
-        <v>Kevian Kraemer</v>
+        <v>paris jackson</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
       </c>
       <c r="L166" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>teenage drama - paris jackson</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>does it still mean something?</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-27</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>only if it matters</v>
       </c>
       <c r="G167" t="str">
-        <v>3:00</v>
+        <v>3:48</v>
       </c>
       <c r="H167" t="str">
-        <v>Ruel</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
       </c>
       <c r="L167" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>does it still mean something? - Kevian Kraemer</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>Debbie Don't Cry</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-27</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>Debbie Don't Cry - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H168" t="str">
-        <v>Cruz Beckham</v>
+        <v>Ruel</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
       </c>
       <c r="L168" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>Debbie Don't Cry - Ruel</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Cotton Flower</v>
+        <v>YEAH YEAH YEAH</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-27</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>YEAH YEAH YEAH - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:53</v>
+        <v>2:25</v>
       </c>
       <c r="H169" t="str">
-        <v>Future Islands</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
       </c>
       <c r="L169" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>YEAH YEAH YEAH - Cruz Beckham</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>Cotton Flower</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-27</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G170" t="str">
-        <v>3:22</v>
+        <v>3:53</v>
       </c>
       <c r="H170" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Future Islands</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
       </c>
       <c r="L170" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>Cotton Flower - Future Islands</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Comfort</v>
+        <v>WAHALA RIDDIM</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-27</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>So Help Me God</v>
+        <v>WAHALA RIDDIM - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>5:35</v>
+        <v>3:22</v>
       </c>
       <c r="H171" t="str">
-        <v>Kelsey Lu</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
       </c>
       <c r="L171" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>WAHALA RIDDIM - THEHONESTGUY</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Skin</v>
+        <v>Comfort</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-27</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Skin - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G172" t="str">
-        <v>3:00</v>
+        <v>5:35</v>
       </c>
       <c r="H172" t="str">
-        <v>Alessi Rose</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/comfort/1876521144</v>
       </c>
       <c r="L172" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>Comfort - Kelsey Lu</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>IDGAF</v>
+        <v>Skin</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-27</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>IDGAF - Single</v>
+        <v>Skin - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:55</v>
+        <v>3:00</v>
       </c>
       <c r="H173" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Alessi Rose</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/skin/1895865252</v>
       </c>
       <c r="L173" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>Skin - Alessi Rose</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Run Rabbit</v>
+        <v>IDGAF</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-27</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>IDGAF - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:09</v>
+        <v>2:55</v>
       </c>
       <c r="H174" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
       </c>
       <c r="L174" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>IDGAF - Katelyn Tarver</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>Run Rabbit</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-27</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>Run Rabbit - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:03</v>
+        <v>3:09</v>
       </c>
       <c r="H175" t="str">
-        <v>CamelPhat</v>
+        <v>Mollie Elizabeth</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
       </c>
       <c r="L175" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>Run Rabbit - Mollie Elizabeth</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>So Good (feat. Kuuda)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-27</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>So Good (feat. Kuuda) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>5:01</v>
+        <v>3:03</v>
       </c>
       <c r="H176" t="str">
-        <v>Lane 8</v>
+        <v>CamelPhat</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
       </c>
       <c r="L176" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>So Good (feat. Kuuda) - CamelPhat</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>regalametutiempo</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-27</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>PROYECTANDO</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="G177" t="str">
-        <v>3:01</v>
+        <v>5:01</v>
       </c>
       <c r="H177" t="str">
-        <v>Julio Caesar</v>
+        <v>Lane 8</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
       </c>
       <c r="L177" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>Empty Theatre, Pretty Picture - Lane 8</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>On Sight</v>
+        <v>regalametutiempo</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-27</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Left on RED</v>
+        <v>PROYECTANDO</v>
       </c>
       <c r="G178" t="str">
-        <v>2:25</v>
+        <v>3:01</v>
       </c>
       <c r="H178" t="str">
-        <v>REMI</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
       </c>
       <c r="L178" t="str">
-        <v>On Sight - REMI</v>
+        <v>regalametutiempo - Julio Caesar</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Masks Off</v>
+        <v>On Sight</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-27</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Masks Off - Single</v>
+        <v>Left on RED</v>
       </c>
       <c r="G179" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H179" t="str">
-        <v>Jesse Welles</v>
+        <v>REMI</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/remi/1716510008</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
       </c>
       <c r="L179" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>On Sight - REMI</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>I'm Just A Girl</v>
+        <v>Masks Off</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-27</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>Masks Off - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H180" t="str">
-        <v>Thee Marloes</v>
+        <v>Jesse Welles</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
       </c>
       <c r="L180" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>Masks Off - Jesse Welles</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>I'm Just A Girl</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-27</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>EXIT 2B</v>
+        <v>Di Hotel Malibu</v>
       </c>
       <c r="G181" t="str">
-        <v>2:11</v>
+        <v>2:49</v>
       </c>
       <c r="H181" t="str">
-        <v>B0YG1RL</v>
+        <v>Thee Marloes</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
       </c>
       <c r="L181" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>I'm Just A Girl - Thee Marloes</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Money Tree</v>
+        <v>Soleil (feat. Isabella Lovestory)</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-27</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Money Tree - Single</v>
+        <v>EXIT 2B</v>
       </c>
       <c r="G182" t="str">
-        <v>2:39</v>
+        <v>2:11</v>
       </c>
       <c r="H182" t="str">
-        <v>Olympia Vitalis</v>
+        <v>B0YG1RL</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
       </c>
       <c r="L182" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Homerunner</v>
+        <v>Money Tree</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-27</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Homerunner - Single</v>
+        <v>Money Tree - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H183" t="str">
-        <v>slayr</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
       </c>
       <c r="L183" t="str">
-        <v>Homerunner - slayr</v>
+        <v>Money Tree - Olympia Vitalis</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Mail</v>
+        <v>Homerunner</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
+        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-27</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Mail - Single</v>
+        <v>Homerunner - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:14</v>
+        <v>2:36</v>
       </c>
       <c r="H184" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
+        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
       </c>
       <c r="L184" t="str">
-        <v>Mail - MexikoDro</v>
+        <v>Homerunner - slayr</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Waste Your Heart</v>
+        <v>Mail</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
+        <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-27</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Waste Your Heart - Single</v>
+        <v>Mail - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:31</v>
+        <v>2:14</v>
       </c>
       <c r="H185" t="str">
-        <v>Magnus Ferrell</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
+        <v>https://music.apple.com/us/album/mail/6769190634</v>
       </c>
       <c r="L185" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
+        <v>Mail - MexikoDro</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Sleeping Pills</v>
+        <v>Waste Your Heart</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
+        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-27</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Sleeping Pills - Single</v>
+        <v>Waste Your Heart - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:03</v>
+        <v>2:31</v>
       </c>
       <c r="H186" t="str">
-        <v>Dolder</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
+        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
       </c>
       <c r="L186" t="str">
-        <v>Sleeping Pills - Dolder</v>
+        <v>Waste Your Heart - Magnus Ferrell</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>KODACHROMATIC</v>
+        <v>Sleeping Pills</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
+        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-27</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>KODACHROMATIC - Single</v>
+        <v>Sleeping Pills - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:53</v>
+        <v>3:03</v>
       </c>
       <c r="H187" t="str">
-        <v>Tiger La Flor</v>
+        <v>Dolder</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
+        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
       </c>
       <c r="L187" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
+        <v>Sleeping Pills - Dolder</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>FOMO</v>
+        <v>KODACHROMATIC</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
+        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-27</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Map Of Her Shadow</v>
+        <v>KODACHROMATIC - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:01</v>
+        <v>2:53</v>
       </c>
       <c r="H188" t="str">
-        <v>Anais Cardot</v>
+        <v>Tiger La Flor</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
+        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
       </c>
       <c r="L188" t="str">
-        <v>FOMO - Anais Cardot</v>
+        <v>KODACHROMATIC - Tiger La Flor</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Black Fire</v>
+        <v>FOMO</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
+        <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-27</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Sulfur Surfer</v>
+        <v>Map Of Her Shadow</v>
       </c>
       <c r="G189" t="str">
-        <v>3:37</v>
+        <v>3:01</v>
       </c>
       <c r="H189" t="str">
-        <v>Bladee</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
+        <v>https://music.apple.com/us/album/fomo/1890190623</v>
       </c>
       <c r="L189" t="str">
-        <v>Black Fire - Bladee</v>
+        <v>FOMO - Anais Cardot</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>As Seen in the Unseen</v>
+        <v>Black Fire</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
+        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-27</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Sulfur Surfer</v>
       </c>
       <c r="G190" t="str">
-        <v>6:59</v>
+        <v>3:37</v>
       </c>
       <c r="H190" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Bladee</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/bladee/861359576</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
+        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
       </c>
       <c r="L190" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
+        <v>Black Fire - Bladee</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Every Man-Any Man</v>
+        <v>As Seen in the Unseen</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
+        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-27</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G191" t="str">
-        <v>4:20</v>
+        <v>6:59</v>
       </c>
       <c r="H191" t="str">
-        <v>Armored Saint</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
+        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
       </c>
       <c r="L191" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
+        <v>As Seen in the Unseen - Dimmu Borgir</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>No Arms</v>
+        <v>Every Man-Any Man</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
+        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-27</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>From A Distance</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G192" t="str">
-        <v>3:43</v>
+        <v>4:20</v>
       </c>
       <c r="H192" t="str">
-        <v>156/Silence</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
+        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
       </c>
       <c r="L192" t="str">
-        <v>No Arms - 156/Silence</v>
+        <v>Every Man-Any Man - Armored Saint</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>It's Neverending</v>
+        <v>No Arms</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
+        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-27</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Neverending</v>
+        <v>From A Distance</v>
       </c>
       <c r="G193" t="str">
-        <v>8:35</v>
+        <v>3:43</v>
       </c>
       <c r="H193" t="str">
-        <v>Monolord</v>
+        <v>156/Silence</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
+        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
       </c>
       <c r="L193" t="str">
-        <v>It's Neverending - Monolord</v>
+        <v>No Arms - 156/Silence</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>The Kids Will Kill Us</v>
+        <v>It's Neverending</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
+        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-27</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>The Kids Will Kill Us - Single</v>
+        <v>Neverending</v>
       </c>
       <c r="G194" t="str">
-        <v>3:45</v>
+        <v>8:35</v>
       </c>
       <c r="H194" t="str">
-        <v>Witch Club Satan</v>
+        <v>Monolord</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
+        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
       </c>
       <c r="L194" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
+        <v>It's Neverending - Monolord</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
+        <v>The Kids Will Kill Us</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
+        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-27</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
+        <v>The Kids Will Kill Us - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:20</v>
+        <v>3:45</v>
       </c>
       <c r="H195" t="str">
-        <v>The Darkness</v>
+        <v>Witch Club Satan</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
+        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
+        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
       </c>
       <c r="L195" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
+        <v>The Kids Will Kill Us - Witch Club Satan</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>All Day</v>
+        <v>Masters of the Universe (from "Masters of the Universe")</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
+        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-27</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Feet On Fire</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:29</v>
+        <v>3:20</v>
       </c>
       <c r="H196" t="str">
-        <v>Ben Chapman</v>
+        <v>The Darkness</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
+        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
+        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
       </c>
       <c r="L196" t="str">
-        <v>All Day - Ben Chapman</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Sigui</v>
+        <v>All Day</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
+        <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-27</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Massa</v>
+        <v>Feet On Fire</v>
       </c>
       <c r="G197" t="str">
-        <v>3:17</v>
+        <v>2:29</v>
       </c>
       <c r="H197" t="str">
-        <v>Fatoumata Diawara</v>
+        <v>Ben Chapman</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
+        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
+        <v>https://music.apple.com/us/album/all-day/1880746349</v>
       </c>
       <c r="L197" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
+        <v>All Day - Ben Chapman</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>High Tail</v>
+        <v>Sigui</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
+        <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-27</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Where the South Winds Wail</v>
+        <v>Massa</v>
       </c>
       <c r="G198" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H198" t="str">
-        <v>Gitkin</v>
+        <v>Fatoumata Diawara</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
+        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
+        <v>https://music.apple.com/us/album/sigui/1890241617</v>
       </c>
       <c r="L198" t="str">
-        <v>High Tail - Gitkin</v>
+        <v>Sigui - Fatoumata Diawara</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Mice Protection</v>
+        <v>High Tail</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-27</v>
@@ -7937,68 +7937,106 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Ugly Duckling Union</v>
+        <v>Where the South Winds Wail</v>
       </c>
       <c r="G199" t="str">
-        <v>3:34</v>
+        <v>2:31</v>
       </c>
       <c r="H199" t="str">
-        <v>Lowertown</v>
+        <v>Gitkin</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
       </c>
       <c r="L199" t="str">
-        <v>Mice Protection - Lowertown</v>
+        <v>High Tail - Gitkin</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
+        <v>Mice Protection</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Ugly Duckling Union</v>
+      </c>
+      <c r="G200" t="str">
+        <v>3:34</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Lowertown</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Mice Protection - Lowertown</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
         <v>Tóxica</v>
       </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
-      <c r="D200" t="str">
-        <v>2026-05-27</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
+      <c r="D201" t="str">
+        <v>2026-05-27</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
         <v>Caribenya</v>
       </c>
-      <c r="G200" t="str">
+      <c r="G201" t="str">
         <v>3:48</v>
       </c>
-      <c r="H200" t="str">
+      <c r="H201" t="str">
         <v>Lido Pimienta</v>
       </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
         <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
       </c>
-      <c r="K200" t="str">
+      <c r="K201" t="str">
         <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
       </c>
-      <c r="L200" t="str">
+      <c r="L201" t="str">
         <v>Tóxica - Lido Pimienta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K</v>
       </c>
       <c r="B2" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
+        <v>https://www.youtube.com/watch?v=fMt-f2aUW3c</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -457,7 +457,7 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>Bruno Mars</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,33 +469,33 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
+        <v>Surreal World of Oddities - Pulling At My Strings - Official Music Video | 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
+        <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
+        <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>15 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Keith Urban</v>
+        <v>Julia Cole Music</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,33 +507,33 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
+        <v>Julia Cole - Love You to Death (Official Video) - Julia Cole Music</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
+        <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Nelly Furtado</v>
+        <v>VictorBiliac</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,33 +545,33 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
+        <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit ) - VictorBiliac</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
+        <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>Teddy Swims and American Music Awards</v>
+        <v>Lolo Zouaï and disiz</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,33 +583,33 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
+        <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video) - Lolo Zouaï and disiz</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
+        <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>4 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
+        <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>4 days ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>Shakira and 2 more</v>
+        <v>Jungle4eva</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,33 +621,33 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
+        <v>Jungle - The Wave (Official Video) - Jungle4eva</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
+        <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>4 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
+        <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4 days ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Lainey Wilson</v>
+        <v>DAYTIME TV</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,33 +659,33 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
+        <v>Daytime TV – Sun (Official Music Video) - DAYTIME TV</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
+        <v>https://www.youtube.com/watch?v=ACNj3L2bzV8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>Duran Duran</v>
+        <v>Kelly Boesch AI Art</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,33 +697,33 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
+        <v>Surreal and Strange AI Video | Not Made For The Cage | Kelly Boesch - 4K - Kelly Boesch AI Art</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nico Santos - Optimist</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B9" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
+        <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>Nico Santos</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,33 +735,33 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Nico Santos - Optimist - Nico Santos</v>
+        <v>Bruno Mars - Risk It All [Live From The Romantic Tour] - Bruno Mars</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B10" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
+        <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>4 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>DEF LEPPARD</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,33 +773,33 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
+        <v>Keith Urban - Summer Breeze (52nd American Music Awards) - Keith Urban</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
+        <v>https://www.youtube.com/watch?v=lHYEMWFuErM</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Will Linley</v>
+        <v>Nelly Furtado</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,33 +811,33 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
+        <v>Nelly Furtado, Boi-1Da, Canada Soccer - ELECTRIC CIRCUS (Official Music Video) - Nelly Furtado</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video)</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs)</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
+        <v>https://www.youtube.com/watch?v=ttM4gWkhZBk</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Kylie Minogue</v>
+        <v>Teddy Swims and American Music Awards</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
+        <v>Teddy Swims - Mr. Know It All (Live from the AMAs) - Teddy Swims and American Music Awards</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
+        <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Billy Raffoul</v>
+        <v>Shakira and 2 more</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
+        <v>Shakira, Burna Boy - Dai Dai (Official Video) - Shakira and 2 more</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
+        <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>The Offspring</v>
+        <v>Lainey Wilson</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
+        <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards) - Lainey Wilson</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B15" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
+        <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>David Gilmour</v>
+        <v>Duran Duran</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
+        <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ] - Duran Duran</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
+        <v>Nico Santos - Optimist</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
+        <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>Scorpions</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
+        <v>Nico Santos - Optimist - Nico Santos</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace)</v>
       </c>
       <c r="B17" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
+        <v>https://www.youtube.com/watch?v=k5SRMgdG4L4</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1027,7 +1027,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>DEF LEPPARD</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
+        <v>Def Leppard - Personal Jesus (Live at Caesars Palace) - DEF LEPPARD</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B18" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
+        <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Kygo and Dan Tyminski</v>
+        <v>Will Linley</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
+        <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer) - Will Linley</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Warning - Ego (Official Video)</v>
+        <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
+        <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1103,7 +1103,7 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>The Warning</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Warning - Ego (Official Video) - The Warning</v>
+        <v>Kylie Minogue - Story (Official Lyric Video) - Kylie Minogue</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>paris jackson - teenage drama (official lyric video)</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
+        <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1141,7 +1141,7 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>paris jackson</v>
+        <v>Billy Raffoul</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
+        <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video) - Billy Raffoul</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B21" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
+        <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1179,7 +1179,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Minelli</v>
+        <v>The Offspring</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
+        <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025) - The Offspring</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B22" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
+        <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1217,7 +1217,7 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Maggie Rose</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
+        <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024) - David Gilmour</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B23" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
+        <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1255,7 +1255,7 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>David Guetta</v>
+        <v>Scorpions</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
+        <v>Scorpions - Delicate Dance (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B24" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
+        <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1293,7 +1293,7 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>Chris Young and Shaylen</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,33 +1305,33 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Lauv - Pretty Little Things</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
+        <v>https://www.youtube.com/watch?v=OKf_IOGxFQo</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>Lauv</v>
+        <v>Kygo and Dan Tyminski</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,33 +1343,33 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Lauv - Pretty Little Things - Lauv</v>
+        <v>Kygo, Dan Tyminski - Heaven On Your Mind (Official Lyric Video) - Kygo and Dan Tyminski</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
+        <v>The Warning - Ego (Official Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
+        <v>https://www.youtube.com/watch?v=CG6Q5i75bR4</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>Icona Pop</v>
+        <v>The Warning</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,33 +1381,33 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
+        <v>The Warning - Ego (Official Video) - The Warning</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Will Swinton - Only One (Official Video)</v>
+        <v>paris jackson - teenage drama (official lyric video)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
+        <v>https://www.youtube.com/watch?v=kVfDArNljos</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Will Swinton</v>
+        <v>paris jackson</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,33 +1419,33 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
+        <v>paris jackson - teenage drama (official lyric video) - paris jackson</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Dean Lewis - Escape (Official Video)</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
+        <v>https://www.youtube.com/watch?v=xOsjm-AwN5I</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Dean Lewis</v>
+        <v>Minelli</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
+        <v>Minelli - Sun Goes Down | Official Visualizer - Minelli</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
+        <v>https://www.youtube.com/watch?v=aWNK-vWrN60</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Dua Lipa and OficialMana</v>
+        <v>Maggie Rose</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
+        <v>Maggie Rose - Gentle Man (Official Studio Video) - Maggie Rose</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video)</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer]</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
+        <v>https://www.youtube.com/watch?v=mN5AZBrVq9I</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Niall Horan</v>
+        <v>David Guetta</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
+        <v>Jennifer Lopez &amp; David Guetta - Save Me Tonight (DJs From Mars remix) [Visualizer] - David Guetta</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
+        <v>https://www.youtube.com/watch?v=0PTufEGRAVQ</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Chris Young and Shaylen</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,33 +1571,33 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
+        <v>Chris Young, Shaylen - One Of Us (Official Lyric Video) - Chris Young and Shaylen</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
+        <v>Lauv - Pretty Little Things</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
+        <v>https://www.youtube.com/watch?v=_JBfanFvHnA</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>RUEL</v>
+        <v>Lauv</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
+        <v>Lauv - Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>TINI - Down (LIVE)</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
+        <v>https://www.youtube.com/watch?v=bXA_Q75QZTs</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>TINI</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,33 +1647,33 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>TINI - Down (LIVE) - TINI</v>
+        <v>Icona Pop - Butterfly Feelings (Official Audio) - Icona Pop</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Charli xcx - SS26 (Official Video)</v>
+        <v>Will Swinton - Only One (Official Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
+        <v>https://www.youtube.com/watch?v=A0KzP-zm9hA</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Charli xcx</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,21 +1685,21 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
+        <v>Will Swinton - Only One (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Dua Lipa - Live From Mexico</v>
+        <v>Dean Lewis - Escape (Official Video)</v>
       </c>
       <c r="B35" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
+        <v>https://www.youtube.com/watch?v=BZRaTXCkhcg</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Dua Lipa</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,21 +1723,21 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
+        <v>Dean Lewis - Escape (Official Video) - Dean Lewis</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico]</v>
       </c>
       <c r="B36" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
+        <v>https://www.youtube.com/watch?v=PNm0hf_zZJY</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1749,7 +1749,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Matilda Mann</v>
+        <v>Dua Lipa and OficialMana</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,21 +1761,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
+        <v>Dua Lipa - Oye Mi Amor (Feat. Fher de Maná) [Live From Mexico] - Dua Lipa and OficialMana</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
+        <v>Niall Horan - End of an Era (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
+        <v>https://www.youtube.com/watch?v=EUNNmAAe5gQ</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1787,7 +1787,7 @@
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Ella Langley</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
+        <v>Niall Horan - End of an Era (Lyric Video) - Niall Horan</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio)</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
+        <v>https://www.youtube.com/watch?v=B402rKl4bUg</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
+        <v>Olivia Rodrigo - the cure (Official Music Video) - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
+        <v>https://www.youtube.com/watch?v=iz7wuk0GOwI</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>kesha</v>
+        <v>RUEL</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
+        <v>Ruel - Debbie Don't Cry (Official Music Video) - RUEL</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
+        <v>TINI - Down (LIVE)</v>
       </c>
       <c r="B40" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
+        <v>https://www.youtube.com/watch?v=ADbFeQUPTrk</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Holly Humberstone</v>
+        <v>TINI</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
+        <v>TINI - Down (LIVE) - TINI</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Foo Fighters - Of All People (Official Video)</v>
+        <v>Charli xcx - SS26 (Official Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
+        <v>https://www.youtube.com/watch?v=twLhSqabby0</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Foo Fighters</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
+        <v>Charli xcx - SS26 (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
+        <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
+        <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>The Analogues</v>
+        <v>Dua Lipa</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,21 +1989,21 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
+        <v>Dua Lipa - Live From Mexico - Dua Lipa</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
+        <v>https://www.youtube.com/watch?v=XPyubkkkw44</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Rod Stewart</v>
+        <v>Matilda Mann</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,21 +2027,21 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
+        <v>Matilda Mann - 'The Fig Tree' (Official Video) - Matilda Mann</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
+        <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Blue October</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,21 +2065,21 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
+        <v>Ella Langley - Be Her (61st Academy of Country Music Awards) - Ella Langley</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Far Caspian - hum (Official Video)</v>
+        <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
+        <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Far Caspian</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,21 +2103,21 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
+        <v>Nothing But Thieves - Evolution (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Kenia Os - Love Bombing</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B46" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
+        <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2129,7 +2129,7 @@
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Kenia Os</v>
+        <v>kesha</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,21 +2141,21 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Kenia Os - Love Bombing - Kenia Os</v>
+        <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO) - kesha</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify</v>
       </c>
       <c r="B47" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
+        <v>https://www.youtube.com/watch?v=_WGsJYCCfU8</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2167,7 +2167,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
+        <v>Holly Humberstone - Cruel World (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
+        <v>Foo Fighters - Of All People (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
+        <v>https://www.youtube.com/watch?v=r_iMzMrCQs0</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Foo Fighters - Of All People (Official Video) - Foo Fighters</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
+        <v>https://www.youtube.com/watch?v=cLiyO2t3xd0</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>The Analogues</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
+        <v>'From Me To You' by The Beatles, performed by The Young Analogues - The Analogues</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video]</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
+        <v>https://www.youtube.com/watch?v=O67Q25sMhyU</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Rod Stewart</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Rod Stewart – It Takes Two (with Tina Turner) [Official Music Video] - Rod Stewart</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
+        <v>https://www.youtube.com/watch?v=tPfbOjz-hRs</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Blue October</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Blue October - 18th Floor Balcony (Official Music Video) - Blue October</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
+        <v>Far Caspian - hum (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
+        <v>https://www.youtube.com/watch?v=qqXrLDhGJRk</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Far Caspian</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
+        <v>Far Caspian - hum (Official Video) - Far Caspian</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
+        <v>Kenia Os - Love Bombing</v>
       </c>
       <c r="B53" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
+        <v>https://www.youtube.com/watch?v=ZuWA3pAyriQ</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>10 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Kenia Os</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
+        <v>Kenia Os - Love Bombing - Kenia Os</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
+        <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Evanescence</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
+        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026 - Purple Disco Machine</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
+        <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>earMUSIC and Deep Purple Official</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,21 +2483,21 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
+        <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹</v>
       </c>
       <c r="B56" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
+        <v>https://www.youtube.com/watch?v=EykAYQj99GU</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2509,7 +2509,7 @@
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Armin van Buuren</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,21 +2521,21 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Celebration! Eurovision at 70 | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​​🇦🇹 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B57" t="str">
         <v>11 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
+        <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2547,7 +2547,7 @@
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Madison Cunningham</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
+        <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
+        <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Johnny Orlando</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
+        <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video)</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
+        <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Carver Jones</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
+        <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video)</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
+        <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Jazmin bean</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,21 +2673,21 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
+        <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​ - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
+        <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2699,7 +2699,7 @@
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Baby Queen</v>
+        <v>Evanescence</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
+        <v>Evanescence – Who Will You Follow (Official Music Video) - Evanescence</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Switchfoot - Absolution (Official Audio)</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
+        <v>https://www.youtube.com/watch?v=SoSr0sStFaE</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Switchfoot</v>
+        <v>earMUSIC and Deep Purple Official</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,33 +2749,33 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
+        <v>DEEP PURPLE – ARROGANT BOY (Official Video) - earMUSIC and Deep Purple Official</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio)</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
+        <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>Grace Potter</v>
+        <v>Armin van Buuren</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,33 +2787,33 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
+        <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video] - Armin van Buuren</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
+        <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Modern Talking Offiziell</v>
+        <v>Madison Cunningham</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
+        <v>Madison Cunningham - "Take Two" (Live in Chicago) - Madison Cunningham</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
+        <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B65" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
+        <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>The All-American Rejects</v>
+        <v>Johnny Orlando</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
+        <v>Johnny Orlando - Heads Up (Official Video) - Johnny Orlando</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser)</v>
+        <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B66" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
+        <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2889,7 +2889,7 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Henry Moodie</v>
+        <v>Carver Jones</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,21 +2901,21 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
+        <v>Carver Jones - BEST FRIEND (Official Video) - Carver Jones</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
+        <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
+        <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2927,7 +2927,7 @@
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Spacey Jane</v>
+        <v>Jazmin bean</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,21 +2939,21 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
+        <v>Jazmin Bean - Darling (Official Music Video) - Jazmin bean</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B68" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
+        <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2965,7 +2965,7 @@
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Megan Moroney</v>
+        <v>Baby Queen</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,21 +2977,21 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
+        <v>Baby Queen - Word Vomit (Official Visualiser) - Baby Queen</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser)</v>
+        <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B69" t="str">
         <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
+        <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Matt Hansen</v>
+        <v>Switchfoot</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,33 +3015,33 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
+        <v>Switchfoot - Absolution (Official Audio) - Switchfoot</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
+        <v>Grace Potter - Love Me Not (Official Audio)</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
+        <v>https://www.youtube.com/watch?v=W3v0HAxDTUY</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Matt Hansen</v>
+        <v>Grace Potter</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,33 +3053,33 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
+        <v>Grace Potter - Love Me Not (Official Audio) - Grace Potter</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Keith Urban - Steal Away (Visualizer)</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986)</v>
       </c>
       <c r="B71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
+        <v>https://www.youtube.com/watch?v=Dhy4xH662vE</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Keith Urban</v>
+        <v>Modern Talking Offiziell</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
+        <v>Modern Talking - Brother Louie (Top Of The Pops, 21.8.1986) - Modern Talking Offiziell</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>VALÉ - Mugshot (Official Video)</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
+        <v>https://www.youtube.com/watch?v=y9axmk3NjrA</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>VALÉ</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
+        <v>The All-American Rejects - Clothesline (Official Lyric Video) - The All-American Rejects</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio)</v>
+        <v>Henry Moodie - MISS U (Official Visualiser)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
+        <v>https://www.youtube.com/watch?v=l_lroRlSmTE</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Mackenzie Carpenter</v>
+        <v>Henry Moodie</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
+        <v>Henry Moodie - MISS U (Official Visualiser) - Henry Moodie</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
+        <v>https://www.youtube.com/watch?v=q6tyEMN5haA</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Towa Bird</v>
+        <v>Spacey Jane</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,33 +3205,33 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
+        <v>Spacey Jane - I Never See Her (Official Music Video) - Spacey Jane</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
+        <v>https://www.youtube.com/watch?v=qacdvCqOZGc</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>Sabrina Sterling</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,33 +3243,33 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
+        <v>Megan Moroney - Traitor (Roles Reversed) (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
+        <v>Matt Hansen - Orchid (Official Visualiser)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
+        <v>https://www.youtube.com/watch?v=otVYamnbOhY</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Little Big Town</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,33 +3281,33 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
+        <v>Matt Hansen - Orchid (Official Visualiser) - Matt Hansen</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Becky G - EPA (Official Video)</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
+        <v>https://www.youtube.com/watch?v=difyagcyKiU</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Becky G</v>
+        <v>Matt Hansen</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,33 +3319,33 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Becky G - EPA (Official Video) - Becky G</v>
+        <v>Matt Hansen - Before We Know It (Lyric Video) - Matt Hansen</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
+        <v>Keith Urban - Steal Away (Visualizer)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
+        <v>https://www.youtube.com/watch?v=WRyi7k-CMvE</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Daisy the Great</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,33 +3357,33 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
+        <v>Keith Urban - Steal Away (Visualizer) - Keith Urban</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Towa Bird - Dog (Official Music Video)</v>
+        <v>VALÉ - Mugshot (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
+        <v>https://www.youtube.com/watch?v=WpaXYUUkLfY</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Towa Bird</v>
+        <v>VALÉ</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,33 +3395,33 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
+        <v>VALÉ - Mugshot (Official Video) - VALÉ</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
+        <v>Mackenzie Carpenter - High Pony (Audio)</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
+        <v>https://www.youtube.com/watch?v=KJWDJ_DVSY0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Madonna</v>
+        <v>Mackenzie Carpenter</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,33 +3433,33 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
+        <v>Mackenzie Carpenter - High Pony (Audio) - Mackenzie Carpenter</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video)</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
+        <v>https://www.youtube.com/watch?v=bkexF61iyvo</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Ally Salort</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,33 +3471,33 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
+        <v>Towa Bird - Afterglow (Official Lyric Video) - Towa Bird</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Bella White - Better - Official Music Video</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
+        <v>https://www.youtube.com/watch?v=8F9vgfGtYcY</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Bella White</v>
+        <v>Sabrina Sterling</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,33 +3509,33 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Bella White - Better - Official Music Video - Bella White</v>
+        <v>Sabrina Sterling - Hold (Official Visualizer) - Sabrina Sterling</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
+        <v>https://www.youtube.com/watch?v=Q4thqUUQ8zw</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Charles Wesley Godwin</v>
+        <v>Little Big Town</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,33 +3547,33 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
+        <v>Little Big Town - Hey There Sunshine (Official Music Video) - Little Big Town</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
+        <v>Becky G - EPA (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
+        <v>https://www.youtube.com/watch?v=5ZmJvlGiF5k</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Towa Bird</v>
+        <v>Becky G</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
+        <v>Becky G - EPA (Official Video) - Becky G</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer)</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
+        <v>https://www.youtube.com/watch?v=FKnLjvlfrGs</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>Miranda Lambert</v>
+        <v>Daisy the Great</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,33 +3623,33 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
+        <v>Daisy the Great - Can I Have A Moment (Official Video) - Daisy the Great</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
+        <v>Towa Bird - Dog (Official Music Video)</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
+        <v>https://www.youtube.com/watch?v=c5Rp_iHpQOQ</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Lady Gaga</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,33 +3661,33 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
+        <v>Towa Bird - Dog (Official Music Video) - Towa Bird</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer]</v>
       </c>
       <c r="B87" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
+        <v>https://www.youtube.com/watch?v=YDTazIuuDPY</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Gracie Abrams</v>
+        <v>Madonna</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,33 +3699,33 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
+        <v>Madonna - I Feel So Free (Peggy Gou Energy Mix) [Official Visualizer] - Madonna</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
+        <v>Ally Salort - Housekeeping (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
+        <v>https://www.youtube.com/watch?v=3SeZO1eCVdI</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,33 +3737,33 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
+        <v>Ally Salort - Housekeeping (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
+        <v>Bella White - Better - Official Music Video</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
+        <v>https://www.youtube.com/watch?v=N224C_h1ILo</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Martin Garrix</v>
+        <v>Bella White</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,21 +3775,21 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
+        <v>Bella White - Better - Official Music Video - Bella White</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Jorja Smith - What's Done Is Done</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
+        <v>https://www.youtube.com/watch?v=1CDiZQKR-zQ</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3801,7 +3801,7 @@
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Jorja Smith</v>
+        <v>Charles Wesley Godwin</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,21 +3813,21 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
+        <v>Charles Wesley Godwin - Better That Way (feat. Luke Combs) (Lyric Video) - Charles Wesley Godwin</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>LP - Shelly (Official Music Video)</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna</v>
       </c>
       <c r="B91" t="str">
         <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
+        <v>https://www.youtube.com/watch?v=uE-cZ2h0omg</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3839,7 +3839,7 @@
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>LP</v>
+        <v>Towa Bird</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>LP - Shelly (Official Music Video) - LP</v>
+        <v>Towa Bird - All Gone (feat. Kathleen Hanna) (Official Lyric Video) ft. Kathleen Hanna - Towa Bird</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
+        <v>Miranda Lambert - Crisco (Visualizer)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
+        <v>https://www.youtube.com/watch?v=14e-s62t5wM</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>The Rolling Stones</v>
+        <v>Miranda Lambert</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
+        <v>Miranda Lambert - Crisco (Visualizer) - Miranda Lambert</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
+        <v>https://www.youtube.com/watch?v=R3gpbT-JZMk</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Oasis</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
+        <v>Lady Gaga - Killah (Apple Music Live 2026) - Lady Gaga</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
+        <v>https://www.youtube.com/watch?v=jFCTQ68gxoY</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>Breaking Benjamin</v>
+        <v>Gracie Abrams</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
+        <v>Gracie Abrams - Hit the Wall (Official Music Video) - Gracie Abrams</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit )</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=yiaqSVpUE3A</v>
+        <v>https://www.youtube.com/watch?v=e76wIbWQLKs</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>VictorBiliac</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Victor Biliac - Si totusi exista iubire ( Cover Edit ) - VictorBiliac</v>
+        <v>The Last Dinner Party - Big Dog (Lyric Video) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Ry_koauoyMQ</v>
+        <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>Linkin Park</v>
+        <v>Martin Garrix</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>From The Inside (Live in Mumbai) - Linkin Park - Linkin Park</v>
+        <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer) - Martin Garrix</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Harry Styles - Dance No More (Official Video)</v>
+        <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
+        <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Harry Styles</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,21 +4079,21 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
+        <v>Jorja Smith - What's Done Is Done - Jorja Smith</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
+        <v>LP - Shelly (Official Music Video)</v>
       </c>
       <c r="B98" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
+        <v>https://www.youtube.com/watch?v=rn8ZONDOfCE</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4105,7 +4105,7 @@
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Eagles</v>
+        <v>LP</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,21 +4117,21 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
+        <v>LP - Shelly (Official Music Video) - LP</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer)</v>
       </c>
       <c r="B99" t="str">
         <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
+        <v>https://www.youtube.com/watch?v=orFUF3JODsU</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4143,7 +4143,7 @@
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Nora Fatehi</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
+        <v>The Rolling Stones - In The Stars (Official Video Trailer) - The Rolling Stones</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser)</v>
       </c>
       <c r="B100" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
+        <v>https://www.youtube.com/watch?v=jYB9fkHHYI4</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Eurovision Song Contest</v>
+        <v>Oasis</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
+        <v>Oasis - Champagne Supernova (Official Visualiser) - Oasis</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
+        <v>https://www.youtube.com/watch?v=4-r0rS903qc</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 months ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Eurovision Song Contest and Alis</v>
+        <v>Breaking Benjamin</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
+        <v>Breaking Benjamin - Something Wicked (Official Audio) - Breaking Benjamin</v>
       </c>
     </row>
     <row r="102">
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/from-down-here/6768357142</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/the-cure/1889992123</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/ss26/6771061782</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/white-flag/1887627840</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/knew-better-part-two/6770601273</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/goals/6769251838</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/we-should-talk/1872842316</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/do-what-you-gotta-do/1887616424</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E201" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L201"/>
+  <dimension ref="A1:L202"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -477,7 +477,7 @@
         <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>15 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>15 hours ago</v>
+        <v>21 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Victor Biliac - De-ai fi tu salcie la mal ( Cover Edit )</v>
       </c>
       <c r="B4" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=v3c0kG-V2zk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Lolo Zouaï - Coquelicot (feat. disiz) (Official Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=-4p6FkrOGT4</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Jungle - The Wave (Official Video)</v>
       </c>
       <c r="B6" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=DW1vUkqNvqQ</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>21 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Daytime TV – Sun (Official Music Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=Jqo4ra_ch-M</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Bruno Mars - Risk It All [Live From The Romantic Tour]</v>
       </c>
       <c r="B9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=aFbueod4reQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Shakira, Burna Boy - Dai Dai (Official Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=fcnDmrtj6Sk</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Lainey Wilson - Can’t Sit Still (Live from the 61st ACM Awards)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=wacpnp83cJg</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Nico Santos - Optimist</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=JA6PIcBeKZ0</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Will Linley - Holding The Line (From the Prime Original Series, Off Campus / Visualizer)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=eWSwy9GU2L8</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Kylie Minogue - Story (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=fv7_1qKo8mg</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Billy Raffoul &amp; Janie Bay - Hold It Against Me (Official Music Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=3KUQx2s1fQc</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>The Offspring - You’re Gonna Go Far Kid | Live Across South America (2025)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=vWf4uiLvwF8</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>David Gilmour - The Piper's Call (Later... with Jools Holland, 2 Nov 2024)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=9xjMaXegmWM</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Scorpions - Delicate Dance (Madison Square Garden 2022)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=yAjEr9WLTnU</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Live From Charleston)</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=oRw4PqBzGc0</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Dua Lipa - Live From Mexico</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=vZYVkitGXBU</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Nothing But Thieves - Evolution (Official Audio)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=Kcs-4EZSUW0</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>KESHA - ORIGAMI! (OFFICIAL MUSIC VIDEO)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=HiLT1jzDZb4</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES MAY 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=ftJR_CrRsig</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Alis - Nân (LIVE) | Albania 🇦🇱 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B57" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=doGkDemPcFE</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Evanescence – Who Will You Follow (Official Music Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=ak4Ti54Y6rY</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Armin van Buuren - Autumn Leaves (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B63" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=9iCw89UajaQ</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Madison Cunningham - "Take Two" (Live in Chicago)</v>
       </c>
       <c r="B64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=bUBLlJXtjqE</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Johnny Orlando - Heads Up (Official Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=s5mClhWsajE</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Carver Jones - BEST FRIEND (Official Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=96xxxpZ5uxI</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Jazmin Bean - Darling (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=N4uW3ZcowBM</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Baby Queen - Word Vomit (Official Visualiser)</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=T-bo4Klq_js</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Switchfoot - Absolution (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=nCOSfMdKq9k</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Jorja Smith - What's Done Is Done</v>
       </c>
       <c r="B97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=hbDcfEhaQBc</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>The Wave</v>
+        <v>Handle</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
+        <v>https://music.apple.com/us/song/handle/6771922623</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-28</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Sunshine</v>
+        <v>Blue Island</v>
       </c>
       <c r="G102" t="str">
-        <v>3:22</v>
+        <v>3:06</v>
       </c>
       <c r="H102" t="str">
-        <v>Jungle</v>
+        <v>Ravyn Lenae</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/jungle/825833522</v>
+        <v>https://music.apple.com/us/artist/ravyn-lenae/1044417443</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
+        <v>https://music.apple.com/us/album/handle/6771922622</v>
       </c>
       <c r="L102" t="str">
-        <v>The Wave - Jungle</v>
+        <v>Handle - Ravyn Lenae</v>
       </c>
     </row>
     <row r="103">
@@ -4502,13 +4502,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>STOP</v>
+        <v>The Wave</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/stop/6771161771</v>
+        <v>https://music.apple.com/us/song/the-wave/1886730541</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-28</v>
@@ -4517,25 +4517,25 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>are you mad at me? - Single</v>
+        <v>Sunshine</v>
       </c>
       <c r="G109" t="str">
-        <v>2:56</v>
+        <v>3:22</v>
       </c>
       <c r="H109" t="str">
-        <v>Bella Kay</v>
+        <v>Jungle</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
+        <v>https://music.apple.com/us/artist/jungle/825833522</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/stop/6771161760</v>
+        <v>https://music.apple.com/us/album/the-wave/1886730527</v>
       </c>
       <c r="L109" t="str">
-        <v>STOP - Bella Kay</v>
+        <v>The Wave - Jungle</v>
       </c>
     </row>
     <row r="110">
@@ -4616,13 +4616,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Ego</v>
+        <v>STOP</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/ego/6769207667</v>
+        <v>https://music.apple.com/us/song/stop/6771161771</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-28</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Ego - Single</v>
+        <v>are you mad at me? - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:53</v>
+        <v>2:56</v>
       </c>
       <c r="H112" t="str">
-        <v>The Warning</v>
+        <v>Bella Kay</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
+        <v>https://music.apple.com/us/artist/bella-kay/1706434165</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/ego/6769207665</v>
+        <v>https://music.apple.com/us/album/stop/6771161760</v>
       </c>
       <c r="L112" t="str">
-        <v>Ego - The Warning</v>
+        <v>STOP - Bella Kay</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie')</v>
+        <v>Ego</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
+        <v>https://music.apple.com/us/song/ego/6769207667</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-28</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
+        <v>Ego - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:17</v>
+        <v>2:53</v>
       </c>
       <c r="H113" t="str">
-        <v>Kylie Minogue</v>
+        <v>The Warning</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
+        <v>https://music.apple.com/us/artist/the-warning/260719953</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
+        <v>https://music.apple.com/us/album/ego/6769207665</v>
       </c>
       <c r="L113" t="str">
-        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
+        <v>Ego - The Warning</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>All That Matters</v>
+        <v>Light up (From the Netflix Documentary 'kylie')</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
+        <v>https://music.apple.com/us/song/light-up-from-the-netflix-documentary-kylie/6768013506</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-28</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Light up (From the Netflix Documentary 'Kylie') - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:43</v>
+        <v>3:17</v>
       </c>
       <c r="H114" t="str">
-        <v>6LACK</v>
+        <v>Kylie Minogue</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/kylie-minogue/465031</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
+        <v>https://music.apple.com/us/album/light-up-from-the-netflix-documentary-kylie/6768013505</v>
       </c>
       <c r="L114" t="str">
-        <v>All That Matters - 6LACK</v>
+        <v>Light up (From the Netflix Documentary 'kylie') - Kylie Minogue</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Like A Virgin</v>
+        <v>All That Matters</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
+        <v>https://music.apple.com/us/song/all-that-matters/1884792161</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-28</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Terrified .</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G115" t="str">
-        <v>2:34</v>
+        <v>3:43</v>
       </c>
       <c r="H115" t="str">
-        <v>fakemink</v>
+        <v>6LACK</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
+        <v>https://music.apple.com/us/album/all-that-matters/1884792154</v>
       </c>
       <c r="L115" t="str">
-        <v>Like A Virgin - fakemink</v>
+        <v>All That Matters - 6LACK</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>24 Hours</v>
+        <v>Like A Virgin</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
+        <v>https://music.apple.com/us/song/like-a-virgin/6768157753</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-28</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>24 Hours - Single</v>
+        <v>Terrified .</v>
       </c>
       <c r="G116" t="str">
-        <v>3:17</v>
+        <v>2:34</v>
       </c>
       <c r="H116" t="str">
-        <v>Stormzy</v>
+        <v>fakemink</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
+        <v>https://music.apple.com/us/artist/fakemink/1744500063</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
+        <v>https://music.apple.com/us/album/like-a-virgin/6768157748</v>
       </c>
       <c r="L116" t="str">
-        <v>24 Hours - Stormzy</v>
+        <v>Like A Virgin - fakemink</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>HOES (From Scary Movie)</v>
+        <v>24 Hours</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
+        <v>https://music.apple.com/us/song/24-hours/6771060076</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-28</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>HOES (From Scary Movie) - Single</v>
+        <v>24 Hours - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:09</v>
+        <v>3:17</v>
       </c>
       <c r="H117" t="str">
-        <v>Lizzo</v>
+        <v>Stormzy</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
+        <v>https://music.apple.com/us/artist/stormzy/394865154</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
+        <v>https://music.apple.com/us/album/24-hours/6771060073</v>
       </c>
       <c r="L117" t="str">
-        <v>HOES (From Scary Movie) - Lizzo</v>
+        <v>24 Hours - Stormzy</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Ms. Tundra</v>
+        <v>HOES (From Scary Movie)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
+        <v>https://music.apple.com/us/song/hoes-from-scary-movie/6770661310</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-28</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Highway 79</v>
+        <v>HOES (From Scary Movie) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:12</v>
+        <v>2:09</v>
       </c>
       <c r="H118" t="str">
-        <v>Ne-Yo</v>
+        <v>Lizzo</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
+        <v>https://music.apple.com/us/artist/lizzo/472949623</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
+        <v>https://music.apple.com/us/album/hoes-from-scary-movie/6770661290</v>
       </c>
       <c r="L118" t="str">
-        <v>Ms. Tundra - Ne-Yo</v>
+        <v>HOES (From Scary Movie) - Lizzo</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>TARENTINO</v>
+        <v>Ms. Tundra</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
+        <v>https://music.apple.com/us/song/ms-tundra/6770614896</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-28</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>TARENTINO - Single</v>
+        <v>Highway 79</v>
       </c>
       <c r="G119" t="str">
-        <v>2:23</v>
+        <v>3:12</v>
       </c>
       <c r="H119" t="str">
-        <v>Labrinth</v>
+        <v>Ne-Yo</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/ne-yo/78257321</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
+        <v>https://music.apple.com/us/album/ms-tundra/6770614875</v>
       </c>
       <c r="L119" t="str">
-        <v>TARENTINO - Labrinth</v>
+        <v>Ms. Tundra - Ne-Yo</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Daydreamin’</v>
+        <v>TARENTINO</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
+        <v>https://music.apple.com/us/song/tarentino/6769927265</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-28</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>KONNAKOL (Deluxe)</v>
+        <v>TARENTINO - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:58</v>
+        <v>2:23</v>
       </c>
       <c r="H120" t="str">
-        <v>ZAYN</v>
+        <v>Labrinth</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
+        <v>https://music.apple.com/us/album/tarentino/6769927262</v>
       </c>
       <c r="L120" t="str">
-        <v>Daydreamin’ - ZAYN</v>
+        <v>TARENTINO - Labrinth</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>End of an Era</v>
+        <v>Daydreamin’</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
+        <v>https://music.apple.com/us/song/daydreamin/6769559461</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-28</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Dinner Party</v>
+        <v>KONNAKOL (Deluxe)</v>
       </c>
       <c r="G121" t="str">
-        <v>3:38</v>
+        <v>2:58</v>
       </c>
       <c r="H121" t="str">
-        <v>Niall Horan</v>
+        <v>ZAYN</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
+        <v>https://music.apple.com/us/album/daydreamin/6769559345</v>
       </c>
       <c r="L121" t="str">
-        <v>End of an Era - Niall Horan</v>
+        <v>Daydreamin’ - ZAYN</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Questions</v>
+        <v>End of an Era</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/questions/1871502847</v>
+        <v>https://music.apple.com/us/song/end-of-an-era/1884418721</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-28</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Florescence</v>
+        <v>Dinner Party</v>
       </c>
       <c r="G122" t="str">
-        <v>3:07</v>
+        <v>3:38</v>
       </c>
       <c r="H122" t="str">
-        <v>Maisie Peters</v>
+        <v>Niall Horan</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
+        <v>https://music.apple.com/us/artist/niall-horan/471260298</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/questions/1871502372</v>
+        <v>https://music.apple.com/us/album/end-of-an-era/1884418567</v>
       </c>
       <c r="L122" t="str">
-        <v>Questions - Maisie Peters</v>
+        <v>End of an Era - Niall Horan</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Heart Has To Work So Hard</v>
+        <v>Questions</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
+        <v>https://music.apple.com/us/song/questions/1871502847</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-28</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Heart Has To Work So Hard - Single</v>
+        <v>Florescence</v>
       </c>
       <c r="G123" t="str">
-        <v>3:12</v>
+        <v>3:07</v>
       </c>
       <c r="H123" t="str">
-        <v>Blondshell</v>
+        <v>Maisie Peters</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
+        <v>https://music.apple.com/us/artist/maisie-peters/1264549322</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
+        <v>https://music.apple.com/us/album/questions/1871502372</v>
       </c>
       <c r="L123" t="str">
-        <v>Heart Has To Work So Hard - Blondshell</v>
+        <v>Questions - Maisie Peters</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
+        <v>Heart Has To Work So Hard</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
+        <v>https://music.apple.com/us/song/heart-has-to-work-so-hard/6765531270</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-28</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
+        <v>Heart Has To Work So Hard - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:44</v>
+        <v>3:12</v>
       </c>
       <c r="H124" t="str">
-        <v>Kygo</v>
+        <v>Blondshell</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/blondshell/1624592688</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
+        <v>https://music.apple.com/us/album/heart-has-to-work-so-hard/1895982147</v>
       </c>
       <c r="L124" t="str">
-        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
+        <v>Heart Has To Work So Hard - Blondshell</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>PERDISTE EL EMMY.</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski)</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
+        <v>https://music.apple.com/us/song/heaven-on-your-mind-feat-dan-tyminski/6769007435</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-28</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>OMAKASE</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>4:03</v>
+        <v>3:44</v>
       </c>
       <c r="H125" t="str">
-        <v>Álvaro Díaz</v>
+        <v>Kygo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
+        <v>https://music.apple.com/us/album/heaven-on-your-mind-feat-dan-tyminski/6769007431</v>
       </c>
       <c r="L125" t="str">
-        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
+        <v>Heaven On Your Mind (feat. Dan Tyminski) - Kygo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Dosis</v>
+        <v>PERDISTE EL EMMY.</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/dosis/6762929729</v>
+        <v>https://music.apple.com/us/song/perdiste-el-emmy/6771082725</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-28</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>DOSIS</v>
+        <v>OMAKASE</v>
       </c>
       <c r="G126" t="str">
-        <v>3:00</v>
+        <v>4:03</v>
       </c>
       <c r="H126" t="str">
-        <v>Xavi</v>
+        <v>Álvaro Díaz</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/%C3%A1lvaro-d%C3%ADaz/7044841</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/dosis/1895081885</v>
+        <v>https://music.apple.com/us/album/perdiste-el-emmy/6771082594</v>
       </c>
       <c r="L126" t="str">
-        <v>Dosis - Xavi</v>
+        <v>PERDISTE EL EMMY. - Álvaro Díaz</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Would U Still Love Me</v>
+        <v>Dosis</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
+        <v>https://music.apple.com/us/song/dosis/6762929729</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-28</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Whitcomb vs. Flores - Single</v>
+        <v>DOSIS</v>
       </c>
       <c r="G127" t="str">
-        <v>2:36</v>
+        <v>3:00</v>
       </c>
       <c r="H127" t="str">
-        <v>Diplo</v>
+        <v>Xavi</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
+        <v>https://music.apple.com/us/album/dosis/1895081885</v>
       </c>
       <c r="L127" t="str">
-        <v>Would U Still Love Me - Diplo</v>
+        <v>Dosis - Xavi</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Saving This Bottle</v>
+        <v>Would U Still Love Me</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
+        <v>https://music.apple.com/us/song/would-u-still-love-me/6769907834</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-28</v>
@@ -5242,7 +5242,7 @@
         <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>3:05</v>
+        <v>2:36</v>
       </c>
       <c r="H128" t="str">
         <v>Diplo</v>
@@ -5254,21 +5254,21 @@
         <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
+        <v>https://music.apple.com/us/album/would-u-still-love-me/6769907832</v>
       </c>
       <c r="L128" t="str">
-        <v>Saving This Bottle - Diplo</v>
+        <v>Would U Still Love Me - Diplo</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>The Climb</v>
+        <v>Saving This Bottle</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
+        <v>https://music.apple.com/us/song/saving-this-bottle/6769907837</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-28</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>The Climb - Single</v>
+        <v>Whitcomb vs. Flores - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:50</v>
+        <v>3:05</v>
       </c>
       <c r="H129" t="str">
-        <v>Bailey Zimmerman</v>
+        <v>Diplo</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
+        <v>https://music.apple.com/us/artist/diplo/1468290871</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
+        <v>https://music.apple.com/us/album/saving-this-bottle/6769907832</v>
       </c>
       <c r="L129" t="str">
-        <v>The Climb - Bailey Zimmerman</v>
+        <v>Saving This Bottle - Diplo</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>everything tatted</v>
+        <v>The Climb</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
+        <v>https://music.apple.com/us/song/the-climb/6769546149</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-28</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>everything tatted - Single</v>
+        <v>The Climb - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:25</v>
+        <v>3:50</v>
       </c>
       <c r="H130" t="str">
-        <v>mgk</v>
+        <v>Bailey Zimmerman</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/mgk/465954501</v>
+        <v>https://music.apple.com/us/artist/bailey-zimmerman/1551033783</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
+        <v>https://music.apple.com/us/album/the-climb/6769546147</v>
       </c>
       <c r="L130" t="str">
-        <v>everything tatted - mgk</v>
+        <v>The Climb - Bailey Zimmerman</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>BOOMPALA</v>
+        <v>everything tatted</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/boompala/1894802726</v>
+        <v>https://music.apple.com/us/song/everything-tatted/6770773607</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-28</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>'PUREFLOW', Pt. 1</v>
+        <v>everything tatted - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:56</v>
+        <v>3:25</v>
       </c>
       <c r="H131" t="str">
-        <v>LE SSERAFIM</v>
+        <v>mgk</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
+        <v>https://music.apple.com/us/artist/mgk/465954501</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/boompala/1894802719</v>
+        <v>https://music.apple.com/us/album/everything-tatted/6770773606</v>
       </c>
       <c r="L131" t="str">
-        <v>BOOMPALA - LE SSERAFIM</v>
+        <v>everything tatted - mgk</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Let Me Be In Your Arms</v>
+        <v>BOOMPALA</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
+        <v>https://music.apple.com/us/song/boompala/1894802726</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-28</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>can we do it all again?</v>
+        <v>'PUREFLOW', Pt. 1</v>
       </c>
       <c r="G132" t="str">
-        <v>3:13</v>
+        <v>2:56</v>
       </c>
       <c r="H132" t="str">
-        <v>Sonny Fodera</v>
+        <v>LE SSERAFIM</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
+        <v>https://music.apple.com/us/artist/le-sserafim/1616740364</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
+        <v>https://music.apple.com/us/album/boompala/1894802719</v>
       </c>
       <c r="L132" t="str">
-        <v>Let Me Be In Your Arms - Sonny Fodera</v>
+        <v>BOOMPALA - LE SSERAFIM</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Eat, Work, Pray</v>
+        <v>Let Me Be In Your Arms</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
+        <v>https://music.apple.com/us/song/let-me-be-in-your-arms/1881610868</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-28</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Eat, Work, Pray - Single</v>
+        <v>can we do it all again?</v>
       </c>
       <c r="G133" t="str">
-        <v>2:28</v>
+        <v>3:13</v>
       </c>
       <c r="H133" t="str">
-        <v>Sheff G</v>
+        <v>Sonny Fodera</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
+        <v>https://music.apple.com/us/artist/sonny-fodera/324128050</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
+        <v>https://music.apple.com/us/album/let-me-be-in-your-arms/1881610862</v>
       </c>
       <c r="L133" t="str">
-        <v>Eat, Work, Pray - Sheff G</v>
+        <v>Let Me Be In Your Arms - Sonny Fodera</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>touch myself</v>
+        <v>Eat, Work, Pray</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
+        <v>https://music.apple.com/us/song/eat-work-pray/6769134494</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-28</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>and all pride aside</v>
+        <v>Eat, Work, Pray - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>4:09</v>
+        <v>2:28</v>
       </c>
       <c r="H134" t="str">
-        <v>kwn</v>
+        <v>Sheff G</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/sheff-g/1256680782</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
+        <v>https://music.apple.com/us/album/eat-work-pray/6769134493</v>
       </c>
       <c r="L134" t="str">
-        <v>touch myself - kwn</v>
+        <v>Eat, Work, Pray - Sheff G</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Comes and Goes</v>
+        <v>touch myself</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
+        <v>https://music.apple.com/us/song/touch-myself/6769881064</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-28</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Comes and Goes - Single</v>
+        <v>and all pride aside</v>
       </c>
       <c r="G135" t="str">
-        <v>4:22</v>
+        <v>4:09</v>
       </c>
       <c r="H135" t="str">
-        <v>KETTAMA</v>
+        <v>kwn</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
+        <v>https://music.apple.com/us/album/touch-myself/6769880663</v>
       </c>
       <c r="L135" t="str">
-        <v>Comes and Goes - KETTAMA</v>
+        <v>touch myself - kwn</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Dear God</v>
+        <v>Comes and Goes</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
+        <v>https://music.apple.com/us/song/comes-and-goes/6766618932</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-28</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Dear God</v>
+        <v>Comes and Goes - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>6:08</v>
+        <v>4:22</v>
       </c>
       <c r="H136" t="str">
-        <v>The Pretty Reckless</v>
+        <v>KETTAMA</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/kettama/1425703970</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
+        <v>https://music.apple.com/us/album/comes-and-goes/6766618930</v>
       </c>
       <c r="L136" t="str">
-        <v>Dear God - The Pretty Reckless</v>
+        <v>Comes and Goes - KETTAMA</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Hexagons</v>
+        <v>Dear God</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
+        <v>https://music.apple.com/us/song/dear-god/1878237813</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-28</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>The Wow! Signal</v>
+        <v>Dear God</v>
       </c>
       <c r="G137" t="str">
-        <v>5:26</v>
+        <v>6:08</v>
       </c>
       <c r="H137" t="str">
-        <v>Muse</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/muse/1093360</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
+        <v>https://music.apple.com/us/album/dear-god/1878237662</v>
       </c>
       <c r="L137" t="str">
-        <v>Hexagons - Muse</v>
+        <v>Dear God - The Pretty Reckless</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Facile-Batiste</v>
+        <v>Hexagons</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
+        <v>https://music.apple.com/us/song/hexagons/1885607736</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-28</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Black Mozart</v>
+        <v>The Wow! Signal</v>
       </c>
       <c r="G138" t="str">
-        <v>4:55</v>
+        <v>5:26</v>
       </c>
       <c r="H138" t="str">
-        <v>Jon Batiste</v>
+        <v>Muse</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/muse/1093360</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
+        <v>https://music.apple.com/us/album/hexagons/1885607338</v>
       </c>
       <c r="L138" t="str">
-        <v>Facile-Batiste - Jon Batiste</v>
+        <v>Hexagons - Muse</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Pop Pop</v>
+        <v>Facile-Batiste</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
+        <v>https://music.apple.com/us/song/facile-batiste/6764654321</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-28</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Pop Pop - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G139" t="str">
-        <v>2:57</v>
+        <v>4:55</v>
       </c>
       <c r="H139" t="str">
-        <v>Channel Tres</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
+        <v>https://music.apple.com/us/album/facile-batiste/1895866355</v>
       </c>
       <c r="L139" t="str">
-        <v>Pop Pop - Channel Tres</v>
+        <v>Facile-Batiste - Jon Batiste</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>One Of Us</v>
+        <v>Pop Pop</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
+        <v>https://music.apple.com/us/song/pop-pop/6766295303</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-28</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>One Of Us - Single</v>
+        <v>Pop Pop - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:35</v>
+        <v>2:57</v>
       </c>
       <c r="H140" t="str">
-        <v>Chris Young</v>
+        <v>Channel Tres</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
+        <v>https://music.apple.com/us/artist/channel-tres/1293846868</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
+        <v>https://music.apple.com/us/album/pop-pop/1896269430</v>
       </c>
       <c r="L140" t="str">
-        <v>One Of Us - Chris Young</v>
+        <v>Pop Pop - Channel Tres</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Sins of the Father</v>
+        <v>One Of Us</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
+        <v>https://music.apple.com/us/song/one-of-us/6763621931</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-28</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Is God Is (Original Motion Picture Soundtrack)</v>
+        <v>One Of Us - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:20</v>
+        <v>3:35</v>
       </c>
       <c r="H141" t="str">
-        <v>Moses Sumney</v>
+        <v>Chris Young</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
+        <v>https://music.apple.com/us/artist/chris-young/4779205</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
+        <v>https://music.apple.com/us/album/one-of-us/1895402922</v>
       </c>
       <c r="L141" t="str">
-        <v>Sins of the Father - Moses Sumney</v>
+        <v>One Of Us - Chris Young</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Life On The Run</v>
+        <v>Sins of the Father</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
+        <v>https://music.apple.com/us/song/sins-of-the-father/6771012711</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-28</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Life On The Run - Single</v>
+        <v>Is God Is (Original Motion Picture Soundtrack)</v>
       </c>
       <c r="G142" t="str">
-        <v>3:49</v>
+        <v>3:20</v>
       </c>
       <c r="H142" t="str">
-        <v>Brandi Carlile</v>
+        <v>Moses Sumney</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
+        <v>https://music.apple.com/us/artist/moses-sumney/843536848</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
+        <v>https://music.apple.com/us/album/sins-of-the-father/6771012707</v>
       </c>
       <c r="L142" t="str">
-        <v>Life On The Run - Brandi Carlile</v>
+        <v>Sins of the Father - Moses Sumney</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>New York Confident</v>
+        <v>Life On The Run</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
+        <v>https://music.apple.com/us/song/life-on-the-run/6766761021</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-28</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>New York Confident - Single</v>
+        <v>Life On The Run - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:27</v>
+        <v>3:49</v>
       </c>
       <c r="H143" t="str">
-        <v>Mark Ambor</v>
+        <v>Brandi Carlile</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
+        <v>https://music.apple.com/us/artist/brandi-carlile/64387579</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
+        <v>https://music.apple.com/us/album/life-on-the-run/6766761019</v>
       </c>
       <c r="L143" t="str">
-        <v>New York Confident - Mark Ambor</v>
+        <v>Life On The Run - Brandi Carlile</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>pequeñita!</v>
+        <v>New York Confident</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
+        <v>https://music.apple.com/us/song/new-york-confident/6765558038</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-28</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>pequeñita! - Single</v>
+        <v>New York Confident - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:39</v>
+        <v>2:27</v>
       </c>
       <c r="H144" t="str">
-        <v>Judeline</v>
+        <v>Mark Ambor</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
+        <v>https://music.apple.com/us/artist/mark-ambor/1459754985</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
+        <v>https://music.apple.com/us/album/new-york-confident/6765558036</v>
       </c>
       <c r="L144" t="str">
-        <v>pequeñita! - Judeline</v>
+        <v>New York Confident - Mark Ambor</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Opaline</v>
+        <v>pequeñita!</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/opaline/1886737060</v>
+        <v>https://music.apple.com/us/song/peque%C3%B1ita/6769827822</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-28</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>pequeñita! - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:17</v>
+        <v>2:39</v>
       </c>
       <c r="H145" t="str">
-        <v>Stephan Moccio</v>
+        <v>Judeline</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/judeline/1487503245</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/opaline/1886736650</v>
+        <v>https://music.apple.com/us/album/peque%C3%B1ita/6769827604</v>
       </c>
       <c r="L145" t="str">
-        <v>Opaline - Stephan Moccio</v>
+        <v>pequeñita! - Judeline</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pretty Little Things</v>
+        <v>Opaline</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
+        <v>https://music.apple.com/us/song/opaline/1886737060</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-28</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Pretty Little Things - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G146" t="str">
-        <v>2:51</v>
+        <v>3:17</v>
       </c>
       <c r="H146" t="str">
-        <v>Lauv</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/lauv/982612996</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
+        <v>https://music.apple.com/us/album/opaline/1886736650</v>
       </c>
       <c r="L146" t="str">
-        <v>Pretty Little Things - Lauv</v>
+        <v>Opaline - Stephan Moccio</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>COLORADO</v>
+        <v>Pretty Little Things</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/colorado/6769065232</v>
+        <v>https://music.apple.com/us/song/pretty-little-things/6767353968</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-28</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>COLORADO - Single</v>
+        <v>Pretty Little Things - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>1:54</v>
+        <v>2:51</v>
       </c>
       <c r="H147" t="str">
-        <v>Loud Luxury</v>
+        <v>Lauv</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
+        <v>https://music.apple.com/us/artist/lauv/982612996</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/colorado/6769064981</v>
+        <v>https://music.apple.com/us/album/pretty-little-things/6767353963</v>
       </c>
       <c r="L147" t="str">
-        <v>COLORADO - Loud Luxury</v>
+        <v>Pretty Little Things - Lauv</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Infidelidad</v>
+        <v>COLORADO</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
+        <v>https://music.apple.com/us/song/colorado/6769065232</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-28</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>El Disco de Salsa</v>
+        <v>COLORADO - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:29</v>
+        <v>1:54</v>
       </c>
       <c r="H148" t="str">
-        <v>Neutro Shorty</v>
+        <v>Loud Luxury</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
+        <v>https://music.apple.com/us/artist/loud-luxury/829284879</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
+        <v>https://music.apple.com/us/album/colorado/6769064981</v>
       </c>
       <c r="L148" t="str">
-        <v>Infidelidad - Neutro Shorty</v>
+        <v>COLORADO - Loud Luxury</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Wrong Place, Wrong time</v>
+        <v>Infidelidad</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
+        <v>https://music.apple.com/us/song/infidelidad/6768853832</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-28</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Y'all Won</v>
+        <v>El Disco de Salsa</v>
       </c>
       <c r="G149" t="str">
-        <v>2:57</v>
+        <v>3:29</v>
       </c>
       <c r="H149" t="str">
-        <v>Veeze</v>
+        <v>Neutro Shorty</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
+        <v>https://music.apple.com/us/artist/neutro-shorty/1066850977</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
+        <v>https://music.apple.com/us/album/infidelidad/6768853655</v>
       </c>
       <c r="L149" t="str">
-        <v>Wrong Place, Wrong time - Veeze</v>
+        <v>Infidelidad - Neutro Shorty</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>La Semana</v>
+        <v>Wrong Place, Wrong time</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
+        <v>https://music.apple.com/us/song/wrong-place-wrong-time/6771554162</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-28</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
+        <v>Y'all Won</v>
       </c>
       <c r="G150" t="str">
-        <v>3:30</v>
+        <v>2:57</v>
       </c>
       <c r="H150" t="str">
-        <v>ELENA ROSE</v>
+        <v>Veeze</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
+        <v>https://music.apple.com/us/artist/veeze/1464999308</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
+        <v>https://music.apple.com/us/album/wrong-place-wrong-time/6771553812</v>
       </c>
       <c r="L150" t="str">
-        <v>La Semana - ELENA ROSE</v>
+        <v>Wrong Place, Wrong time - Veeze</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Una Mujer Como la Suya</v>
+        <v>La Semana</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
+        <v>https://music.apple.com/us/song/la-semana/6769913466</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-28</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Bandera Blanca</v>
+        <v>No Quiero Que Se Acabe Este Bendito Verano - EP</v>
       </c>
       <c r="G151" t="str">
-        <v>3:34</v>
+        <v>3:30</v>
       </c>
       <c r="H151" t="str">
-        <v>Christian Nodal</v>
+        <v>ELENA ROSE</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/elena-rose/1511051551</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
+        <v>https://music.apple.com/us/album/la-semana/6769913464</v>
       </c>
       <c r="L151" t="str">
-        <v>Una Mujer Como la Suya - Christian Nodal</v>
+        <v>La Semana - ELENA ROSE</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Cold</v>
+        <v>Una Mujer Como la Suya</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/cold/6763763802</v>
+        <v>https://music.apple.com/us/song/una-mujer-como-la-suya/6763085035</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-28</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Cold - Single</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G152" t="str">
-        <v>2:52</v>
+        <v>3:34</v>
       </c>
       <c r="H152" t="str">
-        <v>Majid Jordan</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/cold/1895478371</v>
+        <v>https://music.apple.com/us/album/una-mujer-como-la-suya/1895154946</v>
       </c>
       <c r="L152" t="str">
-        <v>Cold - Majid Jordan</v>
+        <v>Una Mujer Como la Suya - Christian Nodal</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>VERTICAL WORLDS</v>
+        <v>Cold</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
+        <v>https://music.apple.com/us/song/cold/6763763802</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-28</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
+        <v>Cold - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:15</v>
+        <v>2:52</v>
       </c>
       <c r="H153" t="str">
-        <v>Ecca Vandal</v>
+        <v>Majid Jordan</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
+        <v>https://music.apple.com/us/artist/majid-jordan/684530590</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
+        <v>https://music.apple.com/us/album/cold/1895478371</v>
       </c>
       <c r="L153" t="str">
-        <v>VERTICAL WORLDS - Ecca Vandal</v>
+        <v>Cold - Majid Jordan</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Child of Divorce</v>
+        <v>VERTICAL WORLDS</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
+        <v>https://music.apple.com/us/song/vertical-worlds/1886485699</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-28</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>soft pop</v>
+        <v>LOOKING FOR PEOPLE TO UNFOLLOW</v>
       </c>
       <c r="G154" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H154" t="str">
-        <v>Amy Shark</v>
+        <v>Ecca Vandal</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/ecca-vandal/878909173</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
+        <v>https://music.apple.com/us/album/vertical-worlds/1886485694</v>
       </c>
       <c r="L154" t="str">
-        <v>Child of Divorce - Amy Shark</v>
+        <v>VERTICAL WORLDS - Ecca Vandal</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Taboo</v>
+        <v>Child of Divorce</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/taboo/6762838716</v>
+        <v>https://music.apple.com/us/song/child-of-divorce/1880496746</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-28</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Taboo - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G155" t="str">
-        <v>3:38</v>
+        <v>3:24</v>
       </c>
       <c r="H155" t="str">
-        <v>Jensen McRae</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/taboo/1895036934</v>
+        <v>https://music.apple.com/us/album/child-of-divorce/1880496743</v>
       </c>
       <c r="L155" t="str">
-        <v>Taboo - Jensen McRae</v>
+        <v>Child of Divorce - Amy Shark</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>I'M OK</v>
+        <v>Taboo</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
+        <v>https://music.apple.com/us/song/taboo/6762838716</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-28</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>A Rii Set</v>
+        <v>Taboo - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:37</v>
+        <v>3:38</v>
       </c>
       <c r="H156" t="str">
-        <v>Pheelz</v>
+        <v>Jensen McRae</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
+        <v>https://music.apple.com/us/artist/jensen-mcrae/591974463</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
+        <v>https://music.apple.com/us/album/taboo/1895036934</v>
       </c>
       <c r="L156" t="str">
-        <v>I'M OK - Pheelz</v>
+        <v>Taboo - Jensen McRae</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Butterfly Feelings</v>
+        <v>I'M OK</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
+        <v>https://music.apple.com/us/song/im-ok/1893392647</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-28</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Ritual</v>
+        <v>A Rii Set</v>
       </c>
       <c r="G157" t="str">
-        <v>2:35</v>
+        <v>2:37</v>
       </c>
       <c r="H157" t="str">
-        <v>Icona Pop</v>
+        <v>Pheelz</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
+        <v>https://music.apple.com/us/artist/pheelz/426470145</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
+        <v>https://music.apple.com/us/album/im-ok/1893392643</v>
       </c>
       <c r="L157" t="str">
-        <v>Butterfly Feelings - Icona Pop</v>
+        <v>I'M OK - Pheelz</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>F**k the DJ</v>
+        <v>Butterfly Feelings</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
+        <v>https://music.apple.com/us/song/butterfly-feelings/1892427232</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-28</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Stage Girl (Not A Dream Anymore)</v>
+        <v>Ritual</v>
       </c>
       <c r="G158" t="str">
-        <v>2:57</v>
+        <v>2:35</v>
       </c>
       <c r="H158" t="str">
-        <v>Eli</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/eli/1802895652</v>
+        <v>https://music.apple.com/us/artist/icona-pop/398345158</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
+        <v>https://music.apple.com/us/album/butterfly-feelings/1892426976</v>
       </c>
       <c r="L158" t="str">
-        <v>F**k the DJ - Eli</v>
+        <v>Butterfly Feelings - Icona Pop</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Grateful</v>
+        <v>F**k the DJ</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/grateful/1887166624</v>
+        <v>https://music.apple.com/us/song/f-k-the-dj/6769903870</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-28</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>24</v>
+        <v>Stage Girl (Not A Dream Anymore)</v>
       </c>
       <c r="G159" t="str">
-        <v>2:18</v>
+        <v>2:57</v>
       </c>
       <c r="H159" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Eli</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/eli/1802895652</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/grateful/1887166427</v>
+        <v>https://music.apple.com/us/album/f-k-the-dj/6769903867</v>
       </c>
       <c r="L159" t="str">
-        <v>Grateful - Alexis Ffrench</v>
+        <v>F**k the DJ - Eli</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Second Chance</v>
+        <v>Grateful</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
+        <v>https://music.apple.com/us/song/grateful/1887166624</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-28</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Second Chance - Single</v>
+        <v>24</v>
       </c>
       <c r="G160" t="str">
-        <v>3:06</v>
+        <v>2:18</v>
       </c>
       <c r="H160" t="str">
-        <v>Lukas Graham</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
+        <v>https://music.apple.com/us/album/grateful/1887166427</v>
       </c>
       <c r="L160" t="str">
-        <v>Second Chance - Lukas Graham</v>
+        <v>Grateful - Alexis Ffrench</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
+        <v>Second Chance</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
+        <v>https://music.apple.com/us/song/second-chance/6766778687</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-28</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Tommyland Rides Again</v>
+        <v>Second Chance - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:49</v>
+        <v>3:06</v>
       </c>
       <c r="H161" t="str">
-        <v>Tommy Lee</v>
+        <v>Lukas Graham</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
+        <v>https://music.apple.com/us/artist/lukas-graham/473219952</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
+        <v>https://music.apple.com/us/album/second-chance/6766778682</v>
       </c>
       <c r="L161" t="str">
-        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
+        <v>Second Chance - Lukas Graham</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>DOOM LOOP</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track]</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
+        <v>https://music.apple.com/us/song/stupid-world-feat-chad-tepper-bonus-track/1893474198</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-28</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Blood Of Your Empire</v>
+        <v>Tommyland Rides Again</v>
       </c>
       <c r="G162" t="str">
-        <v>4:00</v>
+        <v>3:49</v>
       </c>
       <c r="H162" t="str">
-        <v>PRESIDENT</v>
+        <v>Tommy Lee</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/tommy-lee/68696</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
+        <v>https://music.apple.com/us/album/stupid-world-feat-chad-tepper-bonus-track/1893473875</v>
       </c>
       <c r="L162" t="str">
-        <v>DOOM LOOP - PRESIDENT</v>
+        <v>Stupid World (feat. Chad Tepper) [Bonus Track] - Tommy Lee</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>New York City</v>
+        <v>DOOM LOOP</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
+        <v>https://music.apple.com/us/song/doom-loop/6769906140</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-28</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>New York City - Single</v>
+        <v>Blood Of Your Empire</v>
       </c>
       <c r="G163" t="str">
-        <v>3:30</v>
+        <v>4:00</v>
       </c>
       <c r="H163" t="str">
-        <v>Anthony Ramos</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
+        <v>https://music.apple.com/us/album/doom-loop/6769905842</v>
       </c>
       <c r="L163" t="str">
-        <v>New York City - Anthony Ramos</v>
+        <v>DOOM LOOP - PRESIDENT</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>I Found You</v>
+        <v>New York City</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
+        <v>https://music.apple.com/us/song/new-york-city/6770624327</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-28</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>I Found You - Single</v>
+        <v>New York City - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:18</v>
+        <v>3:30</v>
       </c>
       <c r="H164" t="str">
-        <v>TA Thomas</v>
+        <v>Anthony Ramos</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
+        <v>https://music.apple.com/us/artist/anthony-ramos/1313064678</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
+        <v>https://music.apple.com/us/album/new-york-city/6770624324</v>
       </c>
       <c r="L164" t="str">
-        <v>I Found You - TA Thomas</v>
+        <v>New York City - Anthony Ramos</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Just My Type</v>
+        <v>I Found You</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
+        <v>https://music.apple.com/us/song/i-found-you/1894024535</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-28</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Labor Of Love</v>
+        <v>I Found You - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:40</v>
+        <v>3:18</v>
       </c>
       <c r="H165" t="str">
-        <v>Blxst</v>
+        <v>TA Thomas</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
+        <v>https://music.apple.com/us/artist/ta-thomas/1232189106</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
+        <v>https://music.apple.com/us/album/i-found-you/1894024530</v>
       </c>
       <c r="L165" t="str">
-        <v>Just My Type - Blxst</v>
+        <v>I Found You - TA Thomas</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>teenage drama</v>
+        <v>Just My Type</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
+        <v>https://music.apple.com/us/song/just-my-type/6763176089</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-28</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>teenage drama - Single</v>
+        <v>Labor Of Love</v>
       </c>
       <c r="G166" t="str">
-        <v>3:06</v>
+        <v>2:40</v>
       </c>
       <c r="H166" t="str">
-        <v>paris jackson</v>
+        <v>Blxst</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
+        <v>https://music.apple.com/us/artist/blxst/1332205635</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
+        <v>https://music.apple.com/us/album/just-my-type/1895199881</v>
       </c>
       <c r="L166" t="str">
-        <v>teenage drama - paris jackson</v>
+        <v>Just My Type - Blxst</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>does it still mean something?</v>
+        <v>teenage drama</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
+        <v>https://music.apple.com/us/song/teenage-drama/6768447517</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-28</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>only if it matters</v>
+        <v>teenage drama - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:48</v>
+        <v>3:06</v>
       </c>
       <c r="H167" t="str">
-        <v>Kevian Kraemer</v>
+        <v>paris jackson</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/paris-jackson/442691924</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
+        <v>https://music.apple.com/us/album/teenage-drama/6768447515</v>
       </c>
       <c r="L167" t="str">
-        <v>does it still mean something? - Kevian Kraemer</v>
+        <v>teenage drama - paris jackson</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Debbie Don't Cry</v>
+        <v>does it still mean something?</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
+        <v>https://music.apple.com/us/song/does-it-still-mean-something/6768446155</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-28</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Debbie Don't Cry - Single</v>
+        <v>only if it matters</v>
       </c>
       <c r="G168" t="str">
-        <v>3:00</v>
+        <v>3:48</v>
       </c>
       <c r="H168" t="str">
-        <v>Ruel</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
+        <v>https://music.apple.com/us/album/does-it-still-mean-something/6768446154</v>
       </c>
       <c r="L168" t="str">
-        <v>Debbie Don't Cry - Ruel</v>
+        <v>does it still mean something? - Kevian Kraemer</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>YEAH YEAH YEAH</v>
+        <v>Debbie Don't Cry</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
+        <v>https://music.apple.com/us/song/debbie-dont-cry/6768206618</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-28</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>YEAH YEAH YEAH - Single</v>
+        <v>Debbie Don't Cry - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H169" t="str">
-        <v>Cruz Beckham</v>
+        <v>Ruel</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/ruel/1260748364</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
+        <v>https://music.apple.com/us/album/debbie-dont-cry/6768206616</v>
       </c>
       <c r="L169" t="str">
-        <v>YEAH YEAH YEAH - Cruz Beckham</v>
+        <v>Debbie Don't Cry - Ruel</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Cotton Flower</v>
+        <v>YEAH YEAH YEAH</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
+        <v>https://music.apple.com/us/song/yeah-yeah-yeah/6767515615</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-28</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>From a Hole in the Floor to a Fountain of Youth</v>
+        <v>YEAH YEAH YEAH - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:53</v>
+        <v>2:25</v>
       </c>
       <c r="H170" t="str">
-        <v>Future Islands</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
+        <v>https://music.apple.com/us/album/yeah-yeah-yeah/6767515610</v>
       </c>
       <c r="L170" t="str">
-        <v>Cotton Flower - Future Islands</v>
+        <v>YEAH YEAH YEAH - Cruz Beckham</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>WAHALA RIDDIM</v>
+        <v>Cotton Flower</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
+        <v>https://music.apple.com/us/song/cotton-flower/1883045496</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-28</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>WAHALA RIDDIM - Single</v>
+        <v>From a Hole in the Floor to a Fountain of Youth</v>
       </c>
       <c r="G171" t="str">
-        <v>3:22</v>
+        <v>3:53</v>
       </c>
       <c r="H171" t="str">
-        <v>THEHONESTGUY</v>
+        <v>Future Islands</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
+        <v>https://music.apple.com/us/artist/future-islands/288437518</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
+        <v>https://music.apple.com/us/album/cotton-flower/1883045480</v>
       </c>
       <c r="L171" t="str">
-        <v>WAHALA RIDDIM - THEHONESTGUY</v>
+        <v>Cotton Flower - Future Islands</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Comfort</v>
+        <v>WAHALA RIDDIM</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/comfort/1876521401</v>
+        <v>https://music.apple.com/us/song/wahala-riddim/6764504759</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-28</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>So Help Me God</v>
+        <v>WAHALA RIDDIM - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>5:35</v>
+        <v>3:22</v>
       </c>
       <c r="H172" t="str">
-        <v>Kelsey Lu</v>
+        <v>THEHONESTGUY</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
+        <v>https://music.apple.com/us/artist/thehonestguy/1486946139</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/comfort/1876521144</v>
+        <v>https://music.apple.com/us/album/wahala-riddim/1895810537</v>
       </c>
       <c r="L172" t="str">
-        <v>Comfort - Kelsey Lu</v>
+        <v>WAHALA RIDDIM - THEHONESTGUY</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Skin</v>
+        <v>Comfort</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/skin/6764651585</v>
+        <v>https://music.apple.com/us/song/comfort/1876521401</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-28</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Skin - Single</v>
+        <v>So Help Me God</v>
       </c>
       <c r="G173" t="str">
-        <v>3:00</v>
+        <v>5:35</v>
       </c>
       <c r="H173" t="str">
-        <v>Alessi Rose</v>
+        <v>Kelsey Lu</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
+        <v>https://music.apple.com/us/artist/kelsey-lu/575971007</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/skin/1895865252</v>
+        <v>https://music.apple.com/us/album/comfort/1876521144</v>
       </c>
       <c r="L173" t="str">
-        <v>Skin - Alessi Rose</v>
+        <v>Comfort - Kelsey Lu</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>IDGAF</v>
+        <v>Skin</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
+        <v>https://music.apple.com/us/song/skin/6764651585</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-28</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>IDGAF - Single</v>
+        <v>Skin - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:55</v>
+        <v>3:00</v>
       </c>
       <c r="H174" t="str">
-        <v>Katelyn Tarver</v>
+        <v>Alessi Rose</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
+        <v>https://music.apple.com/us/artist/alessi-rose/1628689028</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
+        <v>https://music.apple.com/us/album/skin/1895865252</v>
       </c>
       <c r="L174" t="str">
-        <v>IDGAF - Katelyn Tarver</v>
+        <v>Skin - Alessi Rose</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Run Rabbit</v>
+        <v>IDGAF</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
+        <v>https://music.apple.com/us/song/idgaf/6764422210</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-28</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Run Rabbit - Single</v>
+        <v>IDGAF - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:09</v>
+        <v>2:55</v>
       </c>
       <c r="H175" t="str">
-        <v>Mollie Elizabeth</v>
+        <v>Katelyn Tarver</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
+        <v>https://music.apple.com/us/artist/katelyn-tarver/2356378</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
+        <v>https://music.apple.com/us/album/idgaf/1895773358</v>
       </c>
       <c r="L175" t="str">
-        <v>Run Rabbit - Mollie Elizabeth</v>
+        <v>IDGAF - Katelyn Tarver</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>So Good (feat. Kuuda)</v>
+        <v>Run Rabbit</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
+        <v>https://music.apple.com/us/song/run-rabbit/6767354665</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-28</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>So Good (feat. Kuuda) - Single</v>
+        <v>Run Rabbit - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:03</v>
+        <v>3:09</v>
       </c>
       <c r="H176" t="str">
-        <v>CamelPhat</v>
+        <v>Mollie Elizabeth</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
+        <v>https://music.apple.com/us/artist/mollie-elizabeth/1780515318</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
+        <v>https://music.apple.com/us/album/run-rabbit/6767354664</v>
       </c>
       <c r="L176" t="str">
-        <v>So Good (feat. Kuuda) - CamelPhat</v>
+        <v>Run Rabbit - Mollie Elizabeth</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>So Good (feat. Kuuda)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
+        <v>https://music.apple.com/us/song/so-good-feat-kuuda/6766655966</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-28</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Empty Theatre, Pretty Picture</v>
+        <v>So Good (feat. Kuuda) - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>5:01</v>
+        <v>3:03</v>
       </c>
       <c r="H177" t="str">
-        <v>Lane 8</v>
+        <v>CamelPhat</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
+        <v>https://music.apple.com/us/artist/camelphat/385810888</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
+        <v>https://music.apple.com/us/album/so-good-feat-kuuda/6766655768</v>
       </c>
       <c r="L177" t="str">
-        <v>Empty Theatre, Pretty Picture - Lane 8</v>
+        <v>So Good (feat. Kuuda) - CamelPhat</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>regalametutiempo</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
+        <v>https://music.apple.com/us/song/empty-theatre-pretty-picture/6763608121</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-28</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>PROYECTANDO</v>
+        <v>Empty Theatre, Pretty Picture</v>
       </c>
       <c r="G178" t="str">
-        <v>3:01</v>
+        <v>5:01</v>
       </c>
       <c r="H178" t="str">
-        <v>Julio Caesar</v>
+        <v>Lane 8</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
+        <v>https://music.apple.com/us/artist/lane-8/634763116</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
+        <v>https://music.apple.com/us/album/empty-theatre-pretty-picture/1895395993</v>
       </c>
       <c r="L178" t="str">
-        <v>regalametutiempo - Julio Caesar</v>
+        <v>Empty Theatre, Pretty Picture - Lane 8</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>On Sight</v>
+        <v>regalametutiempo</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
+        <v>https://music.apple.com/us/song/regalametutiempo/6769922877</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-28</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Left on RED</v>
+        <v>PROYECTANDO</v>
       </c>
       <c r="G179" t="str">
-        <v>2:25</v>
+        <v>3:01</v>
       </c>
       <c r="H179" t="str">
-        <v>REMI</v>
+        <v>Julio Caesar</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/remi/1716510008</v>
+        <v>https://music.apple.com/us/artist/julio-caesar/1743513862</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
+        <v>https://music.apple.com/us/album/regalametutiempo/6769922866</v>
       </c>
       <c r="L179" t="str">
-        <v>On Sight - REMI</v>
+        <v>regalametutiempo - Julio Caesar</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Masks Off</v>
+        <v>On Sight</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
+        <v>https://music.apple.com/us/song/on-sight/6763971220</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-28</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Masks Off - Single</v>
+        <v>Left on RED</v>
       </c>
       <c r="G180" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H180" t="str">
-        <v>Jesse Welles</v>
+        <v>REMI</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
+        <v>https://music.apple.com/us/artist/remi/1716510008</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
+        <v>https://music.apple.com/us/album/on-sight/1895580736</v>
       </c>
       <c r="L180" t="str">
-        <v>Masks Off - Jesse Welles</v>
+        <v>On Sight - REMI</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>I'm Just A Girl</v>
+        <v>Masks Off</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
+        <v>https://music.apple.com/us/song/masks-off/6764077133</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-28</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Di Hotel Malibu</v>
+        <v>Masks Off - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H181" t="str">
-        <v>Thee Marloes</v>
+        <v>Jesse Welles</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
+        <v>https://music.apple.com/us/artist/jesse-welles/1737507146</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
+        <v>https://music.apple.com/us/album/masks-off/1895628310</v>
       </c>
       <c r="L181" t="str">
-        <v>I'm Just A Girl - Thee Marloes</v>
+        <v>Masks Off - Jesse Welles</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Soleil (feat. Isabella Lovestory)</v>
+        <v>I'm Just A Girl</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
+        <v>https://music.apple.com/us/song/im-just-a-girl/1878399878</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-28</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>EXIT 2B</v>
+        <v>Di Hotel Malibu</v>
       </c>
       <c r="G182" t="str">
-        <v>2:11</v>
+        <v>2:49</v>
       </c>
       <c r="H182" t="str">
-        <v>B0YG1RL</v>
+        <v>Thee Marloes</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
+        <v>https://music.apple.com/us/artist/thee-marloes/1541376632</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
+        <v>https://music.apple.com/us/album/im-just-a-girl/1878399768</v>
       </c>
       <c r="L182" t="str">
-        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
+        <v>I'm Just A Girl - Thee Marloes</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Money Tree</v>
+        <v>Soleil (feat. Isabella Lovestory)</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
+        <v>https://music.apple.com/us/song/soleil-feat-isabella-lovestory/6769526348</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-28</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Money Tree - Single</v>
+        <v>EXIT 2B</v>
       </c>
       <c r="G183" t="str">
-        <v>2:39</v>
+        <v>2:11</v>
       </c>
       <c r="H183" t="str">
-        <v>Olympia Vitalis</v>
+        <v>B0YG1RL</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
+        <v>https://music.apple.com/us/artist/b0yg1rl/1847766665</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
+        <v>https://music.apple.com/us/album/soleil-feat-isabella-lovestory/6769526101</v>
       </c>
       <c r="L183" t="str">
-        <v>Money Tree - Olympia Vitalis</v>
+        <v>Soleil (feat. Isabella Lovestory) - B0YG1RL</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Homerunner</v>
+        <v>Money Tree</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
+        <v>https://music.apple.com/us/song/money-tree/6763211637</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-28</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Homerunner - Single</v>
+        <v>Money Tree - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H184" t="str">
-        <v>slayr</v>
+        <v>Olympia Vitalis</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
+        <v>https://music.apple.com/us/artist/olympia-vitalis/1588530024</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
+        <v>https://music.apple.com/us/album/money-tree/1895216986</v>
       </c>
       <c r="L184" t="str">
-        <v>Homerunner - slayr</v>
+        <v>Money Tree - Olympia Vitalis</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Mail</v>
+        <v>Homerunner</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/mail/6769190635</v>
+        <v>https://music.apple.com/us/song/homerunner/6770682178</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-28</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Mail - Single</v>
+        <v>Homerunner - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:14</v>
+        <v>2:36</v>
       </c>
       <c r="H185" t="str">
-        <v>MexikoDro</v>
+        <v>slayr</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/slayr/1676805496</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/mail/6769190634</v>
+        <v>https://music.apple.com/us/album/homerunner/6770682177</v>
       </c>
       <c r="L185" t="str">
-        <v>Mail - MexikoDro</v>
+        <v>Homerunner - slayr</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Waste Your Heart</v>
+        <v>Mail</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
+        <v>https://music.apple.com/us/song/mail/6769190635</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-28</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Waste Your Heart - Single</v>
+        <v>Mail - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:31</v>
+        <v>2:14</v>
       </c>
       <c r="H186" t="str">
-        <v>Magnus Ferrell</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
+        <v>https://music.apple.com/us/album/mail/6769190634</v>
       </c>
       <c r="L186" t="str">
-        <v>Waste Your Heart - Magnus Ferrell</v>
+        <v>Mail - MexikoDro</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Sleeping Pills</v>
+        <v>Waste Your Heart</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
+        <v>https://music.apple.com/us/song/waste-your-heart/6769241918</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-28</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Sleeping Pills - Single</v>
+        <v>Waste Your Heart - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:03</v>
+        <v>2:31</v>
       </c>
       <c r="H187" t="str">
-        <v>Dolder</v>
+        <v>Magnus Ferrell</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/magnus-ferrell/1572955044</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
+        <v>https://music.apple.com/us/album/waste-your-heart/6769241913</v>
       </c>
       <c r="L187" t="str">
-        <v>Sleeping Pills - Dolder</v>
+        <v>Waste Your Heart - Magnus Ferrell</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>KODACHROMATIC</v>
+        <v>Sleeping Pills</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
+        <v>https://music.apple.com/us/song/sleeping-pills/6767271675</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-28</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>KODACHROMATIC - Single</v>
+        <v>Sleeping Pills - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:53</v>
+        <v>3:03</v>
       </c>
       <c r="H188" t="str">
-        <v>Tiger La Flor</v>
+        <v>Dolder</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
+        <v>https://music.apple.com/us/album/sleeping-pills/1896452689</v>
       </c>
       <c r="L188" t="str">
-        <v>KODACHROMATIC - Tiger La Flor</v>
+        <v>Sleeping Pills - Dolder</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>FOMO</v>
+        <v>KODACHROMATIC</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/fomo/1890190631</v>
+        <v>https://music.apple.com/us/song/kodachromatic/6770724727</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-28</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Map Of Her Shadow</v>
+        <v>KODACHROMATIC - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:01</v>
+        <v>2:53</v>
       </c>
       <c r="H189" t="str">
-        <v>Anais Cardot</v>
+        <v>Tiger La Flor</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/tiger-la-flor/1613113982</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/fomo/1890190623</v>
+        <v>https://music.apple.com/us/album/kodachromatic/6770724719</v>
       </c>
       <c r="L189" t="str">
-        <v>FOMO - Anais Cardot</v>
+        <v>KODACHROMATIC - Tiger La Flor</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Black Fire</v>
+        <v>FOMO</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
+        <v>https://music.apple.com/us/song/fomo/1890190631</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-28</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Sulfur Surfer</v>
+        <v>Map Of Her Shadow</v>
       </c>
       <c r="G190" t="str">
-        <v>3:37</v>
+        <v>3:01</v>
       </c>
       <c r="H190" t="str">
-        <v>Bladee</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/bladee/861359576</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
+        <v>https://music.apple.com/us/album/fomo/1890190623</v>
       </c>
       <c r="L190" t="str">
-        <v>Black Fire - Bladee</v>
+        <v>FOMO - Anais Cardot</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>As Seen in the Unseen</v>
+        <v>Black Fire</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
+        <v>https://music.apple.com/us/song/black-fire/6770696877</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-28</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Grand Serpent Rising</v>
+        <v>Sulfur Surfer</v>
       </c>
       <c r="G191" t="str">
-        <v>6:59</v>
+        <v>3:37</v>
       </c>
       <c r="H191" t="str">
-        <v>Dimmu Borgir</v>
+        <v>Bladee</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
+        <v>https://music.apple.com/us/artist/bladee/861359576</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
+        <v>https://music.apple.com/us/album/black-fire/6770696743</v>
       </c>
       <c r="L191" t="str">
-        <v>As Seen in the Unseen - Dimmu Borgir</v>
+        <v>Black Fire - Bladee</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Every Man-Any Man</v>
+        <v>As Seen in the Unseen</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
+        <v>https://music.apple.com/us/song/as-seen-in-the-unseen/1883121664</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-28</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Emotion Factory Reset</v>
+        <v>Grand Serpent Rising</v>
       </c>
       <c r="G192" t="str">
-        <v>4:20</v>
+        <v>6:59</v>
       </c>
       <c r="H192" t="str">
-        <v>Armored Saint</v>
+        <v>Dimmu Borgir</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
+        <v>https://music.apple.com/us/artist/dimmu-borgir/15621683</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
+        <v>https://music.apple.com/us/album/as-seen-in-the-unseen/1883121436</v>
       </c>
       <c r="L192" t="str">
-        <v>Every Man-Any Man - Armored Saint</v>
+        <v>As Seen in the Unseen - Dimmu Borgir</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>No Arms</v>
+        <v>Every Man-Any Man</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
+        <v>https://music.apple.com/us/song/every-man-any-man/1872193862</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-28</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>From A Distance</v>
+        <v>Emotion Factory Reset</v>
       </c>
       <c r="G193" t="str">
-        <v>3:43</v>
+        <v>4:20</v>
       </c>
       <c r="H193" t="str">
-        <v>156/Silence</v>
+        <v>Armored Saint</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
+        <v>https://music.apple.com/us/artist/armored-saint/54261072</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
+        <v>https://music.apple.com/us/album/every-man-any-man/1872193859</v>
       </c>
       <c r="L193" t="str">
-        <v>No Arms - 156/Silence</v>
+        <v>Every Man-Any Man - Armored Saint</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>It's Neverending</v>
+        <v>No Arms</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
+        <v>https://music.apple.com/us/song/no-arms/6765776563</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-28</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Neverending</v>
+        <v>From A Distance</v>
       </c>
       <c r="G194" t="str">
-        <v>8:35</v>
+        <v>3:43</v>
       </c>
       <c r="H194" t="str">
-        <v>Monolord</v>
+        <v>156/Silence</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/monolord/833749384</v>
+        <v>https://music.apple.com/us/artist/156-silence/1071395282</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
+        <v>https://music.apple.com/us/album/no-arms/1896069437</v>
       </c>
       <c r="L194" t="str">
-        <v>It's Neverending - Monolord</v>
+        <v>No Arms - 156/Silence</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>The Kids Will Kill Us</v>
+        <v>It's Neverending</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
+        <v>https://music.apple.com/us/song/its-neverending/1871212122</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-28</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>The Kids Will Kill Us - Single</v>
+        <v>Neverending</v>
       </c>
       <c r="G195" t="str">
-        <v>3:45</v>
+        <v>8:35</v>
       </c>
       <c r="H195" t="str">
-        <v>Witch Club Satan</v>
+        <v>Monolord</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
+        <v>https://music.apple.com/us/artist/monolord/833749384</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
+        <v>https://music.apple.com/us/album/its-neverending/1871211801</v>
       </c>
       <c r="L195" t="str">
-        <v>The Kids Will Kill Us - Witch Club Satan</v>
+        <v>It's Neverending - Monolord</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe")</v>
+        <v>The Kids Will Kill Us</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
+        <v>https://music.apple.com/us/song/the-kids-will-kill-us/6766343277</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-28</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
+        <v>The Kids Will Kill Us - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:20</v>
+        <v>3:45</v>
       </c>
       <c r="H196" t="str">
-        <v>The Darkness</v>
+        <v>Witch Club Satan</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
+        <v>https://music.apple.com/us/artist/witch-club-satan/1626477576</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
+        <v>https://music.apple.com/us/album/the-kids-will-kill-us/6766343272</v>
       </c>
       <c r="L196" t="str">
-        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
+        <v>The Kids Will Kill Us - Witch Club Satan</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>All Day</v>
+        <v>Masters of the Universe (from "Masters of the Universe")</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/all-day/1880746584</v>
+        <v>https://music.apple.com/us/song/masters-of-the-universe-from-masters-of-the-universe/6769065783</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-28</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Feet On Fire</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:29</v>
+        <v>3:20</v>
       </c>
       <c r="H197" t="str">
-        <v>Ben Chapman</v>
+        <v>The Darkness</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
+        <v>https://music.apple.com/us/artist/the-darkness/2417388</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/all-day/1880746349</v>
+        <v>https://music.apple.com/us/album/masters-of-the-universe-from-masters-of-the-universe/6769065779</v>
       </c>
       <c r="L197" t="str">
-        <v>All Day - Ben Chapman</v>
+        <v>Masters of the Universe (from "Masters of the Universe") - The Darkness</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Sigui</v>
+        <v>All Day</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/sigui/1890241955</v>
+        <v>https://music.apple.com/us/song/all-day/1880746584</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-28</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Massa</v>
+        <v>Feet On Fire</v>
       </c>
       <c r="G198" t="str">
-        <v>3:17</v>
+        <v>2:29</v>
       </c>
       <c r="H198" t="str">
-        <v>Fatoumata Diawara</v>
+        <v>Ben Chapman</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
+        <v>https://music.apple.com/us/artist/ben-chapman/1581192612</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/sigui/1890241617</v>
+        <v>https://music.apple.com/us/album/all-day/1880746349</v>
       </c>
       <c r="L198" t="str">
-        <v>Sigui - Fatoumata Diawara</v>
+        <v>All Day - Ben Chapman</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>High Tail</v>
+        <v>Sigui</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
+        <v>https://music.apple.com/us/song/sigui/1890241955</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-28</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Where the South Winds Wail</v>
+        <v>Massa</v>
       </c>
       <c r="G199" t="str">
-        <v>2:31</v>
+        <v>3:17</v>
       </c>
       <c r="H199" t="str">
-        <v>Gitkin</v>
+        <v>Fatoumata Diawara</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
+        <v>https://music.apple.com/us/artist/fatoumata-diawara/466213610</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
+        <v>https://music.apple.com/us/album/sigui/1890241617</v>
       </c>
       <c r="L199" t="str">
-        <v>High Tail - Gitkin</v>
+        <v>Sigui - Fatoumata Diawara</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Mice Protection</v>
+        <v>High Tail</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+        <v>https://music.apple.com/us/song/high-tail/1870432994</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-28</v>
@@ -7975,68 +7975,106 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Ugly Duckling Union</v>
+        <v>Where the South Winds Wail</v>
       </c>
       <c r="G200" t="str">
-        <v>3:34</v>
+        <v>2:31</v>
       </c>
       <c r="H200" t="str">
-        <v>Lowertown</v>
+        <v>Gitkin</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+        <v>https://music.apple.com/us/artist/gitkin/1345281815</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+        <v>https://music.apple.com/us/album/high-tail/1870432670</v>
       </c>
       <c r="L200" t="str">
-        <v>Mice Protection - Lowertown</v>
+        <v>High Tail - Gitkin</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
+        <v>Mice Protection</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/mice-protection/1872171972</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>Ugly Duckling Union</v>
+      </c>
+      <c r="G201" t="str">
+        <v>3:34</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Lowertown</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/lowertown/1448207323</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/mice-protection/1872171971</v>
+      </c>
+      <c r="L201" t="str">
+        <v>Mice Protection - Lowertown</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
         <v>Tóxica</v>
       </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
         <v>https://music.apple.com/us/song/t%C3%B3xica/6763056240</v>
       </c>
-      <c r="D201" t="str">
-        <v>2026-05-28</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
+      <c r="D202" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
         <v>Caribenya</v>
       </c>
-      <c r="G201" t="str">
+      <c r="G202" t="str">
         <v>3:48</v>
       </c>
-      <c r="H201" t="str">
+      <c r="H202" t="str">
         <v>Lido Pimienta</v>
       </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
         <v>https://music.apple.com/us/artist/lido-pimienta/389475023</v>
       </c>
-      <c r="K201" t="str">
+      <c r="K202" t="str">
         <v>https://music.apple.com/us/album/t%C3%B3xica/1895141218</v>
       </c>
-      <c r="L201" t="str">
+      <c r="L202" t="str">
         <v>Tóxica - Lido Pimienta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week04/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Julia Cole - Love You to Death (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=dWgmFc2QuLY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>21 hours ago</v>
+        <v>23 hours ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Keith Urban - Summer Breeze (52nd American Music Awards)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=zn-4eVoqofQ</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Duran Duran - "Free to Love," Horse Meat Disco remix. [Video edit Martin Zompicciatti ]</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=w8FTnkNVmq0</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Ella Langley - Be Her (61st Academy of Country Music Awards)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=4KbYfH7EAm8</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>DARA - Bangaranga (LIVE) | Bulgaria 🇧🇬 | Grand Final | Winner of Eurovision 2026</v>
       </c>
       <c r="B55" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=EltgrumKJfk</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Sal Da Vinci - Per Sempre Sì (LIVE) | Italy 🇮🇹 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B58" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=rNpFNJLhSfA</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Alexandra Căpitănescu - Choke Me (LIVE) | Romania 🇷🇴 | Grand Final | Eurovision 2026</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=TpMQ6dhcvvE</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Parov Stelar - Black Lilies (LIVE) | Interval Act | Grand Final | Eurovision 2026 | #UnitedByMusic ​</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=ppCyj5DxO8s</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Martin Garrix &amp; Ed Sheeran - Repeat It (Visualizer)</v>
       </c>
       <c r="B96" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=fdBAvsmh8T4</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
